--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_beverage_soft.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.179364153397734</v>
+        <v>0.1789678794295795</v>
       </c>
       <c r="C2">
-        <v>387.4747747284283</v>
+        <v>385.0811430932134</v>
       </c>
       <c r="D2">
-        <v>382.8847747284283</v>
+        <v>384.0241430932134</v>
       </c>
       <c r="E2">
-        <v>-82</v>
+        <v>-78.467</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.533</v>
       </c>
       <c r="G2">
         <v>4.59</v>
@@ -1451,28 +1451,28 @@
         <v>43.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1777099</v>
       </c>
       <c r="N2">
-        <v>43.2</v>
+        <v>43.02229009999999</v>
       </c>
       <c r="O2">
-        <v>10.368</v>
+        <v>10.325349624</v>
       </c>
       <c r="P2">
-        <v>32.83199999999999</v>
+        <v>32.69694047599999</v>
       </c>
       <c r="Q2">
-        <v>41.632</v>
+        <v>41.496940476</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.179364153397734</v>
+        <v>0.1803894943733126</v>
       </c>
       <c r="T2">
-        <v>0.6562503962404382</v>
+        <v>0.6612882780701629</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>243.0928158757615</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1789678794295795</v>
+        <v>0.1785716054614249</v>
       </c>
       <c r="C3">
-        <v>385.0811430932134</v>
+        <v>382.6943126414527</v>
       </c>
       <c r="D3">
-        <v>384.0241430932134</v>
+        <v>385.1703126414527</v>
       </c>
       <c r="E3">
-        <v>-78.467</v>
+        <v>-74.934</v>
       </c>
       <c r="F3">
-        <v>3.533</v>
+        <v>7.066000000000001</v>
       </c>
       <c r="G3">
         <v>4.59</v>
@@ -1533,28 +1533,28 @@
         <v>43.2</v>
       </c>
       <c r="M3">
-        <v>0.1777099</v>
+        <v>0.3554198</v>
       </c>
       <c r="N3">
-        <v>43.02229009999999</v>
+        <v>42.8445802</v>
       </c>
       <c r="O3">
-        <v>10.325349624</v>
+        <v>10.282699248</v>
       </c>
       <c r="P3">
-        <v>32.69694047599999</v>
+        <v>32.561880952</v>
       </c>
       <c r="Q3">
-        <v>41.496940476</v>
+        <v>41.361880952</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1803894943733126</v>
+        <v>0.1814357606749234</v>
       </c>
       <c r="T3">
-        <v>0.6612882780701629</v>
+        <v>0.6664289738147797</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>243.0928158757615</v>
+        <v>121.5464079378808</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1785716054614249</v>
+        <v>0.1781753314932703</v>
       </c>
       <c r="C4">
-        <v>382.6943126414527</v>
+        <v>380.3143444524703</v>
       </c>
       <c r="D4">
-        <v>385.1703126414527</v>
+        <v>386.3233444524703</v>
       </c>
       <c r="E4">
-        <v>-74.934</v>
+        <v>-71.401</v>
       </c>
       <c r="F4">
-        <v>7.066000000000001</v>
+        <v>10.599</v>
       </c>
       <c r="G4">
         <v>4.59</v>
@@ -1615,28 +1615,28 @@
         <v>43.2</v>
       </c>
       <c r="M4">
-        <v>0.3554198</v>
+        <v>0.5331296999999999</v>
       </c>
       <c r="N4">
-        <v>42.8445802</v>
+        <v>42.6668703</v>
       </c>
       <c r="O4">
-        <v>10.282699248</v>
+        <v>10.240048872</v>
       </c>
       <c r="P4">
-        <v>32.561880952</v>
+        <v>32.426821428</v>
       </c>
       <c r="Q4">
-        <v>41.361880952</v>
+        <v>41.226821428</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1814357606749234</v>
+        <v>0.1825035994775983</v>
       </c>
       <c r="T4">
-        <v>0.6664289738147797</v>
+        <v>0.6716756632860899</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>121.5464079378808</v>
+        <v>81.03093862525387</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1781753314932703</v>
+        <v>0.1777790575251158</v>
       </c>
       <c r="C5">
-        <v>380.3143444524703</v>
+        <v>377.9413003391669</v>
       </c>
       <c r="D5">
-        <v>386.3233444524703</v>
+        <v>387.4833003391669</v>
       </c>
       <c r="E5">
-        <v>-71.401</v>
+        <v>-67.86799999999999</v>
       </c>
       <c r="F5">
-        <v>10.599</v>
+        <v>14.132</v>
       </c>
       <c r="G5">
         <v>4.59</v>
@@ -1697,28 +1697,28 @@
         <v>43.2</v>
       </c>
       <c r="M5">
-        <v>0.5331296999999999</v>
+        <v>0.7108396</v>
       </c>
       <c r="N5">
-        <v>42.6668703</v>
+        <v>42.4891604</v>
       </c>
       <c r="O5">
-        <v>10.240048872</v>
+        <v>10.197398496</v>
       </c>
       <c r="P5">
-        <v>32.426821428</v>
+        <v>32.291761904</v>
       </c>
       <c r="Q5">
-        <v>41.226821428</v>
+        <v>41.091761904</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1825035994775983</v>
+        <v>0.1835936849219956</v>
       </c>
       <c r="T5">
-        <v>0.6716756632860899</v>
+        <v>0.6770316587880522</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>81.03093862525387</v>
+        <v>60.77320396894039</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1777790575251158</v>
+        <v>0.1773827835569612</v>
       </c>
       <c r="C6">
-        <v>377.9413003391669</v>
+        <v>375.575242859064</v>
       </c>
       <c r="D6">
-        <v>387.4833003391669</v>
+        <v>388.650242859064</v>
       </c>
       <c r="E6">
-        <v>-67.86799999999999</v>
+        <v>-64.33499999999999</v>
       </c>
       <c r="F6">
-        <v>14.132</v>
+        <v>17.665</v>
       </c>
       <c r="G6">
         <v>4.59</v>
@@ -1779,28 +1779,28 @@
         <v>43.2</v>
       </c>
       <c r="M6">
-        <v>0.7108396</v>
+        <v>0.8885495000000001</v>
       </c>
       <c r="N6">
-        <v>42.4891604</v>
+        <v>42.31145049999999</v>
       </c>
       <c r="O6">
-        <v>10.197398496</v>
+        <v>10.15474812</v>
       </c>
       <c r="P6">
-        <v>32.291761904</v>
+        <v>32.15670238</v>
       </c>
       <c r="Q6">
-        <v>41.091761904</v>
+        <v>40.95670238</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1835936849219956</v>
+        <v>0.1847067195336434</v>
       </c>
       <c r="T6">
-        <v>0.6770316587880522</v>
+        <v>0.6825004120900557</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>60.77320396894039</v>
+        <v>48.6185631751523</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1773827835569612</v>
+        <v>0.1769865095888066</v>
       </c>
       <c r="C7">
-        <v>375.575242859064</v>
+        <v>373.2162353255511</v>
       </c>
       <c r="D7">
-        <v>388.650242859064</v>
+        <v>389.8242353255511</v>
       </c>
       <c r="E7">
-        <v>-64.33499999999999</v>
+        <v>-60.80199999999999</v>
       </c>
       <c r="F7">
-        <v>17.665</v>
+        <v>21.198</v>
       </c>
       <c r="G7">
         <v>4.59</v>
@@ -1861,28 +1861,28 @@
         <v>43.2</v>
       </c>
       <c r="M7">
-        <v>0.8885495000000001</v>
+        <v>1.0662594</v>
       </c>
       <c r="N7">
-        <v>42.31145049999999</v>
+        <v>42.1337406</v>
       </c>
       <c r="O7">
-        <v>10.15474812</v>
+        <v>10.112097744</v>
       </c>
       <c r="P7">
-        <v>32.15670238</v>
+        <v>32.021642856</v>
       </c>
       <c r="Q7">
-        <v>40.95670238</v>
+        <v>40.821642856</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1847067195336434</v>
+        <v>0.185843435732773</v>
       </c>
       <c r="T7">
-        <v>0.6825004120900557</v>
+        <v>0.6880855218452936</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>48.6185631751523</v>
+        <v>40.51546931262692</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1769865095888066</v>
+        <v>0.1765902356206521</v>
       </c>
       <c r="C8">
-        <v>373.2162353255511</v>
+        <v>370.8643418193364</v>
       </c>
       <c r="D8">
-        <v>389.8242353255511</v>
+        <v>391.0053418193364</v>
       </c>
       <c r="E8">
-        <v>-60.802</v>
+        <v>-57.26900000000001</v>
       </c>
       <c r="F8">
-        <v>21.198</v>
+        <v>24.731</v>
       </c>
       <c r="G8">
         <v>4.59</v>
@@ -1943,28 +1943,28 @@
         <v>43.2</v>
       </c>
       <c r="M8">
-        <v>1.0662594</v>
+        <v>1.2439693</v>
       </c>
       <c r="N8">
-        <v>42.1337406</v>
+        <v>41.9560307</v>
       </c>
       <c r="O8">
-        <v>10.112097744</v>
+        <v>10.069447368</v>
       </c>
       <c r="P8">
-        <v>32.021642856</v>
+        <v>31.886583332</v>
       </c>
       <c r="Q8">
-        <v>40.821642856</v>
+        <v>40.686583332</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.185843435732773</v>
+        <v>0.1870045974415614</v>
       </c>
       <c r="T8">
-        <v>0.6880855218452936</v>
+        <v>0.6937907414877407</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>40.51546931262693</v>
+        <v>34.7275451251088</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1765902356206521</v>
+        <v>0.1761939616524975</v>
       </c>
       <c r="C9">
-        <v>370.8643418193365</v>
+        <v>368.5196272001068</v>
       </c>
       <c r="D9">
-        <v>391.0053418193365</v>
+        <v>392.1936272001068</v>
       </c>
       <c r="E9">
-        <v>-57.269</v>
+        <v>-53.736</v>
       </c>
       <c r="F9">
-        <v>24.731</v>
+        <v>28.264</v>
       </c>
       <c r="G9">
         <v>4.59</v>
@@ -2025,28 +2025,28 @@
         <v>43.2</v>
       </c>
       <c r="M9">
-        <v>1.2439693</v>
+        <v>1.4216792</v>
       </c>
       <c r="N9">
-        <v>41.95603069999999</v>
+        <v>41.7783208</v>
       </c>
       <c r="O9">
-        <v>10.069447368</v>
+        <v>10.026796992</v>
       </c>
       <c r="P9">
-        <v>31.88658333199999</v>
+        <v>31.75152380799999</v>
       </c>
       <c r="Q9">
-        <v>40.686583332</v>
+        <v>40.551523808</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1870045974415614</v>
+        <v>0.1881910017961929</v>
       </c>
       <c r="T9">
-        <v>0.6937907414877407</v>
+        <v>0.6996199876441541</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>34.72754512510879</v>
+        <v>30.38660198447019</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1761939616524975</v>
+        <v>0.175797687684343</v>
       </c>
       <c r="C10">
-        <v>368.5196272001068</v>
+        <v>366.1821571183995</v>
       </c>
       <c r="D10">
-        <v>392.1936272001068</v>
+        <v>393.3891571183995</v>
       </c>
       <c r="E10">
-        <v>-53.736</v>
+        <v>-50.203</v>
       </c>
       <c r="F10">
-        <v>28.264</v>
+        <v>31.797</v>
       </c>
       <c r="G10">
         <v>4.59</v>
@@ -2107,28 +2107,28 @@
         <v>43.2</v>
       </c>
       <c r="M10">
-        <v>1.4216792</v>
+        <v>1.5993891</v>
       </c>
       <c r="N10">
-        <v>41.7783208</v>
+        <v>41.60061089999999</v>
       </c>
       <c r="O10">
-        <v>10.026796992</v>
+        <v>9.984146615999999</v>
       </c>
       <c r="P10">
-        <v>31.75152380799999</v>
+        <v>31.616464284</v>
       </c>
       <c r="Q10">
-        <v>40.551523808</v>
+        <v>40.416464284</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1881910017961929</v>
+        <v>0.1894034809718054</v>
       </c>
       <c r="T10">
-        <v>0.6996199876441541</v>
+        <v>0.7055773491007085</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>30.38660198447019</v>
+        <v>27.01031287508461</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.175797687684343</v>
+        <v>0.1754014137161884</v>
       </c>
       <c r="C11">
-        <v>366.1821571183995</v>
+        <v>363.8519980276944</v>
       </c>
       <c r="D11">
-        <v>393.3891571183995</v>
+        <v>394.5919980276944</v>
       </c>
       <c r="E11">
-        <v>-50.203</v>
+        <v>-46.67</v>
       </c>
       <c r="F11">
-        <v>31.797</v>
+        <v>35.33</v>
       </c>
       <c r="G11">
         <v>4.59</v>
@@ -2189,28 +2189,28 @@
         <v>43.2</v>
       </c>
       <c r="M11">
-        <v>1.5993891</v>
+        <v>1.777099</v>
       </c>
       <c r="N11">
-        <v>41.60061089999999</v>
+        <v>41.422901</v>
       </c>
       <c r="O11">
-        <v>9.984146615999999</v>
+        <v>9.941496239999999</v>
       </c>
       <c r="P11">
-        <v>31.616464284</v>
+        <v>31.48140476</v>
       </c>
       <c r="Q11">
-        <v>40.416464284</v>
+        <v>40.28140476</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1894034809718054</v>
+        <v>0.1906429041290982</v>
       </c>
       <c r="T11">
-        <v>0.7055773491007085</v>
+        <v>0.7116670963674087</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>27.01031287508461</v>
+        <v>24.30928158757616</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1754014137161884</v>
+        <v>0.1750051397480338</v>
       </c>
       <c r="C12">
-        <v>363.8519980276944</v>
+        <v>361.529217196726</v>
       </c>
       <c r="D12">
-        <v>394.5919980276944</v>
+        <v>395.802217196726</v>
       </c>
       <c r="E12">
-        <v>-46.66999999999999</v>
+        <v>-43.137</v>
       </c>
       <c r="F12">
-        <v>35.33000000000001</v>
+        <v>38.863</v>
       </c>
       <c r="G12">
         <v>4.59</v>
@@ -2271,28 +2271,28 @@
         <v>43.2</v>
       </c>
       <c r="M12">
-        <v>1.777099</v>
+        <v>1.9548089</v>
       </c>
       <c r="N12">
-        <v>41.422901</v>
+        <v>41.24519109999999</v>
       </c>
       <c r="O12">
-        <v>9.941496239999999</v>
+        <v>9.898845863999998</v>
       </c>
       <c r="P12">
-        <v>31.48140476</v>
+        <v>31.34634523599999</v>
       </c>
       <c r="Q12">
-        <v>40.28140476</v>
+        <v>40.146345236</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1906429041290982</v>
+        <v>0.1919101794921728</v>
       </c>
       <c r="T12">
-        <v>0.7116670963674087</v>
+        <v>0.7178936918872929</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.30928158757615</v>
+        <v>22.0993468977965</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1750051397480338</v>
+        <v>0.1746088657798793</v>
       </c>
       <c r="C13">
-        <v>361.529217196726</v>
+        <v>359.213882722024</v>
       </c>
       <c r="D13">
-        <v>395.802217196726</v>
+        <v>397.0198827220241</v>
       </c>
       <c r="E13">
-        <v>-43.137</v>
+        <v>-39.604</v>
       </c>
       <c r="F13">
-        <v>38.863</v>
+        <v>42.396</v>
       </c>
       <c r="G13">
         <v>4.59</v>
@@ -2353,28 +2353,28 @@
         <v>43.2</v>
       </c>
       <c r="M13">
-        <v>1.9548089</v>
+        <v>2.1325188</v>
       </c>
       <c r="N13">
-        <v>41.24519109999999</v>
+        <v>41.0674812</v>
       </c>
       <c r="O13">
-        <v>9.898845863999998</v>
+        <v>9.856195487999999</v>
       </c>
       <c r="P13">
-        <v>31.34634523599999</v>
+        <v>31.211285712</v>
       </c>
       <c r="Q13">
-        <v>40.146345236</v>
+        <v>40.011285712</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1919101794921728</v>
+        <v>0.1932062565680446</v>
       </c>
       <c r="T13">
-        <v>0.7178936918872929</v>
+        <v>0.72426180094172</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>22.0993468977965</v>
+        <v>20.25773465631346</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1746088657798793</v>
+        <v>0.1742125918117247</v>
       </c>
       <c r="C14">
-        <v>359.213882722024</v>
+        <v>356.9060635406871</v>
       </c>
       <c r="D14">
-        <v>397.0198827220241</v>
+        <v>398.2450635406871</v>
       </c>
       <c r="E14">
-        <v>-39.604</v>
+        <v>-36.071</v>
       </c>
       <c r="F14">
-        <v>42.396</v>
+        <v>45.929</v>
       </c>
       <c r="G14">
         <v>4.59</v>
@@ -2435,28 +2435,28 @@
         <v>43.2</v>
       </c>
       <c r="M14">
-        <v>2.1325188</v>
+        <v>2.3102287</v>
       </c>
       <c r="N14">
-        <v>41.0674812</v>
+        <v>40.88977129999999</v>
       </c>
       <c r="O14">
-        <v>9.856195487999999</v>
+        <v>9.813545111999998</v>
       </c>
       <c r="P14">
-        <v>31.211285712</v>
+        <v>31.07622618799999</v>
       </c>
       <c r="Q14">
-        <v>40.011285712</v>
+        <v>39.876226188</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1932062565680446</v>
+        <v>0.1945321285192238</v>
       </c>
       <c r="T14">
-        <v>0.72426180094172</v>
+        <v>0.7307763033077432</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.25773465631346</v>
+        <v>18.69944737505858</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1742125918117247</v>
+        <v>0.1738163178435702</v>
       </c>
       <c r="C15">
-        <v>356.9060635406871</v>
+        <v>354.6058294433907</v>
       </c>
       <c r="D15">
-        <v>398.2450635406871</v>
+        <v>399.4778294433908</v>
       </c>
       <c r="E15">
-        <v>-36.071</v>
+        <v>-32.538</v>
       </c>
       <c r="F15">
-        <v>45.929</v>
+        <v>49.462</v>
       </c>
       <c r="G15">
         <v>4.59</v>
@@ -2517,28 +2517,28 @@
         <v>43.2</v>
       </c>
       <c r="M15">
-        <v>2.3102287</v>
+        <v>2.4879386</v>
       </c>
       <c r="N15">
-        <v>40.88977129999999</v>
+        <v>40.7120614</v>
       </c>
       <c r="O15">
-        <v>9.813545111999998</v>
+        <v>9.770894735999999</v>
       </c>
       <c r="P15">
-        <v>31.07622618799999</v>
+        <v>30.941166664</v>
       </c>
       <c r="Q15">
-        <v>39.876226188</v>
+        <v>39.741166664</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1945321285192238</v>
+        <v>0.1958888347018257</v>
       </c>
       <c r="T15">
-        <v>0.7307763033077432</v>
+        <v>0.7374423057287901</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.69944737505858</v>
+        <v>17.3637725625544</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1738163178435702</v>
+        <v>0.1734200438754156</v>
       </c>
       <c r="C16">
-        <v>354.6058294433907</v>
+        <v>352.3132510876416</v>
       </c>
       <c r="D16">
-        <v>399.4778294433908</v>
+        <v>400.7182510876416</v>
       </c>
       <c r="E16">
-        <v>-32.538</v>
+        <v>-29.00499999999999</v>
       </c>
       <c r="F16">
-        <v>49.462</v>
+        <v>52.99500000000001</v>
       </c>
       <c r="G16">
         <v>4.59</v>
@@ -2599,28 +2599,28 @@
         <v>43.2</v>
       </c>
       <c r="M16">
-        <v>2.4879386</v>
+        <v>2.665648500000001</v>
       </c>
       <c r="N16">
-        <v>40.7120614</v>
+        <v>40.53435149999999</v>
       </c>
       <c r="O16">
-        <v>9.770894735999999</v>
+        <v>9.728244359999998</v>
       </c>
       <c r="P16">
-        <v>30.941166664</v>
+        <v>30.80610713999999</v>
       </c>
       <c r="Q16">
-        <v>39.741166664</v>
+        <v>39.60610714</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1958888347018257</v>
+        <v>0.1972774633828419</v>
       </c>
       <c r="T16">
-        <v>0.7374423057287901</v>
+        <v>0.7442651552656265</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.3637725625544</v>
+        <v>16.20618772505077</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1734200438754156</v>
+        <v>0.173023769907261</v>
       </c>
       <c r="C17">
-        <v>352.3132510876416</v>
+        <v>350.0284000112759</v>
       </c>
       <c r="D17">
-        <v>400.7182510876416</v>
+        <v>401.966400011276</v>
       </c>
       <c r="E17">
-        <v>-29.005</v>
+        <v>-25.47199999999999</v>
       </c>
       <c r="F17">
-        <v>52.995</v>
+        <v>56.52800000000001</v>
       </c>
       <c r="G17">
         <v>4.59</v>
@@ -2681,28 +2681,28 @@
         <v>43.2</v>
       </c>
       <c r="M17">
-        <v>2.6656485</v>
+        <v>2.8433584</v>
       </c>
       <c r="N17">
-        <v>40.5343515</v>
+        <v>40.3566416</v>
       </c>
       <c r="O17">
-        <v>9.72824436</v>
+        <v>9.685593983999999</v>
       </c>
       <c r="P17">
-        <v>30.80610714</v>
+        <v>30.671047616</v>
       </c>
       <c r="Q17">
-        <v>39.60610714000001</v>
+        <v>39.471047616</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1972774633828419</v>
+        <v>0.1986991546515012</v>
       </c>
       <c r="T17">
-        <v>0.7442651552656264</v>
+        <v>0.7512504536009589</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.20618772505077</v>
+        <v>15.1933009922351</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.173023769907261</v>
+        <v>0.1726274959391065</v>
       </c>
       <c r="C18">
-        <v>350.0284000112759</v>
+        <v>347.7513486462136</v>
       </c>
       <c r="D18">
-        <v>401.966400011276</v>
+        <v>403.2223486462136</v>
       </c>
       <c r="E18">
-        <v>-25.47199999999999</v>
+        <v>-21.93899999999999</v>
       </c>
       <c r="F18">
-        <v>56.52800000000001</v>
+        <v>60.06100000000001</v>
       </c>
       <c r="G18">
         <v>4.59</v>
@@ -2763,28 +2763,28 @@
         <v>43.2</v>
       </c>
       <c r="M18">
-        <v>2.8433584</v>
+        <v>3.0210683</v>
       </c>
       <c r="N18">
-        <v>40.3566416</v>
+        <v>40.17893169999999</v>
       </c>
       <c r="O18">
-        <v>9.685593983999999</v>
+        <v>9.642943607999998</v>
       </c>
       <c r="P18">
-        <v>30.671047616</v>
+        <v>30.535988092</v>
       </c>
       <c r="Q18">
-        <v>39.471047616</v>
+        <v>39.335988092</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1986991546515012</v>
+        <v>0.2001551035410921</v>
       </c>
       <c r="T18">
-        <v>0.7512504536009589</v>
+        <v>0.7584040723781065</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.1933009922351</v>
+        <v>14.29957740445656</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1726274959391065</v>
+        <v>0.1722312219709519</v>
       </c>
       <c r="C19">
-        <v>347.7513486462136</v>
+        <v>345.4821703324687</v>
       </c>
       <c r="D19">
-        <v>403.2223486462136</v>
+        <v>404.4861703324688</v>
       </c>
       <c r="E19">
-        <v>-21.93899999999999</v>
+        <v>-18.40599999999999</v>
       </c>
       <c r="F19">
-        <v>60.06100000000001</v>
+        <v>63.59400000000001</v>
       </c>
       <c r="G19">
         <v>4.59</v>
@@ -2845,28 +2845,28 @@
         <v>43.2</v>
       </c>
       <c r="M19">
-        <v>3.0210683</v>
+        <v>3.1987782</v>
       </c>
       <c r="N19">
-        <v>40.17893169999999</v>
+        <v>40.0012218</v>
       </c>
       <c r="O19">
-        <v>9.642943607999998</v>
+        <v>9.600293231999999</v>
       </c>
       <c r="P19">
-        <v>30.535988092</v>
+        <v>30.400928568</v>
       </c>
       <c r="Q19">
-        <v>39.335988092</v>
+        <v>39.200928568</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2001551035410921</v>
+        <v>0.2016465633792097</v>
       </c>
       <c r="T19">
-        <v>0.7584040723781065</v>
+        <v>0.7657321696620139</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.29957740445656</v>
+        <v>13.50515643754231</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1722312219709519</v>
+        <v>0.1720515480027973</v>
       </c>
       <c r="C20">
-        <v>345.4821703324687</v>
+        <v>342.5248118706277</v>
       </c>
       <c r="D20">
-        <v>404.4861703324688</v>
+        <v>405.0618118706277</v>
       </c>
       <c r="E20">
-        <v>-18.406</v>
+        <v>-14.87299999999999</v>
       </c>
       <c r="F20">
-        <v>63.594</v>
+        <v>67.12700000000001</v>
       </c>
       <c r="G20">
         <v>4.59</v>
@@ -2927,45 +2927,45 @@
         <v>43.2</v>
       </c>
       <c r="M20">
-        <v>3.1987782</v>
+        <v>3.4771786</v>
       </c>
       <c r="N20">
-        <v>40.0012218</v>
+        <v>39.72282139999999</v>
       </c>
       <c r="O20">
-        <v>9.600293231999999</v>
+        <v>9.533477135999998</v>
       </c>
       <c r="P20">
-        <v>30.400928568</v>
+        <v>30.189344264</v>
       </c>
       <c r="Q20">
-        <v>39.200928568</v>
+        <v>38.989344264</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2016465633792096</v>
+        <v>0.2031748493861696</v>
       </c>
       <c r="T20">
-        <v>0.7657321696620137</v>
+        <v>0.7732412076195978</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.24</v>
       </c>
       <c r="W20">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>13.50515643754231</v>
+        <v>12.42386571687747</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1720515480027973</v>
+        <v>0.1716666740346428</v>
       </c>
       <c r="C21">
-        <v>342.5248118706277</v>
+        <v>340.2304061854311</v>
       </c>
       <c r="D21">
-        <v>405.0618118706277</v>
+        <v>406.3004061854311</v>
       </c>
       <c r="E21">
-        <v>-14.87299999999999</v>
+        <v>-11.33999999999999</v>
       </c>
       <c r="F21">
-        <v>67.12700000000001</v>
+        <v>70.66000000000001</v>
       </c>
       <c r="G21">
         <v>4.59</v>
@@ -3009,28 +3009,28 @@
         <v>43.2</v>
       </c>
       <c r="M21">
-        <v>3.4771786</v>
+        <v>3.660188000000001</v>
       </c>
       <c r="N21">
-        <v>39.72282139999999</v>
+        <v>39.539812</v>
       </c>
       <c r="O21">
-        <v>9.533477135999998</v>
+        <v>9.489554879999998</v>
       </c>
       <c r="P21">
-        <v>30.189344264</v>
+        <v>30.05025712</v>
       </c>
       <c r="Q21">
-        <v>38.989344264</v>
+        <v>38.85025712</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2031748493861696</v>
+        <v>0.2047413425433035</v>
       </c>
       <c r="T21">
-        <v>0.7732412076195978</v>
+        <v>0.7809379715261214</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.42386571687747</v>
+        <v>11.80267243103359</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1716666740346428</v>
+        <v>0.1712818000664882</v>
       </c>
       <c r="C22">
-        <v>340.2304061854311</v>
+        <v>337.9435984580041</v>
       </c>
       <c r="D22">
-        <v>406.3004061854311</v>
+        <v>407.5465984580042</v>
       </c>
       <c r="E22">
-        <v>-11.33999999999999</v>
+        <v>-7.806999999999988</v>
       </c>
       <c r="F22">
-        <v>70.66000000000001</v>
+        <v>74.19300000000001</v>
       </c>
       <c r="G22">
         <v>4.59</v>
@@ -3091,28 +3091,28 @@
         <v>43.2</v>
       </c>
       <c r="M22">
-        <v>3.660188000000001</v>
+        <v>3.843197400000001</v>
       </c>
       <c r="N22">
-        <v>39.539812</v>
+        <v>39.35680259999999</v>
       </c>
       <c r="O22">
-        <v>9.489554879999998</v>
+        <v>9.445632623999998</v>
       </c>
       <c r="P22">
-        <v>30.05025712</v>
+        <v>29.911169976</v>
       </c>
       <c r="Q22">
-        <v>38.85025712</v>
+        <v>38.711169976</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2047413425433035</v>
+        <v>0.2063474937550484</v>
       </c>
       <c r="T22">
-        <v>0.7809379715261214</v>
+        <v>0.7888295902150888</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.80267243103359</v>
+        <v>11.24064041050818</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1712818000664882</v>
+        <v>0.1708969260983337</v>
       </c>
       <c r="C23">
-        <v>337.9435984580041</v>
+        <v>335.6644588161165</v>
       </c>
       <c r="D23">
-        <v>407.5465984580042</v>
+        <v>408.8004588161165</v>
       </c>
       <c r="E23">
-        <v>-7.807000000000002</v>
+        <v>-4.274000000000001</v>
       </c>
       <c r="F23">
-        <v>74.193</v>
+        <v>77.726</v>
       </c>
       <c r="G23">
         <v>4.59</v>
@@ -3173,28 +3173,28 @@
         <v>43.2</v>
       </c>
       <c r="M23">
-        <v>3.8431974</v>
+        <v>4.0262068</v>
       </c>
       <c r="N23">
-        <v>39.35680259999999</v>
+        <v>39.1737932</v>
       </c>
       <c r="O23">
-        <v>9.445632623999998</v>
+        <v>9.401710368</v>
       </c>
       <c r="P23">
-        <v>29.911169976</v>
+        <v>29.772082832</v>
       </c>
       <c r="Q23">
-        <v>38.711169976</v>
+        <v>38.57208283200001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2063474937550484</v>
+        <v>0.207994828331197</v>
       </c>
       <c r="T23">
-        <v>0.7888295902150888</v>
+        <v>0.7969235581012092</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.24064041050819</v>
+        <v>10.72970221003054</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1708969260983337</v>
+        <v>0.1705120521301791</v>
       </c>
       <c r="C24">
-        <v>335.6644588161165</v>
+        <v>333.393058253224</v>
       </c>
       <c r="D24">
-        <v>408.8004588161165</v>
+        <v>410.0620582532241</v>
       </c>
       <c r="E24">
-        <v>-4.274000000000001</v>
+        <v>-0.7409999999999997</v>
       </c>
       <c r="F24">
-        <v>77.726</v>
+        <v>81.259</v>
       </c>
       <c r="G24">
         <v>4.59</v>
@@ -3255,28 +3255,28 @@
         <v>43.2</v>
       </c>
       <c r="M24">
-        <v>4.0262068</v>
+        <v>4.2092162</v>
       </c>
       <c r="N24">
-        <v>39.1737932</v>
+        <v>38.9907838</v>
       </c>
       <c r="O24">
-        <v>9.401710368</v>
+        <v>9.357788111999998</v>
       </c>
       <c r="P24">
-        <v>29.772082832</v>
+        <v>29.632995688</v>
       </c>
       <c r="Q24">
-        <v>38.57208283200001</v>
+        <v>38.43299568800001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.207994828331197</v>
+        <v>0.2096849508184144</v>
       </c>
       <c r="T24">
-        <v>0.7969235581012092</v>
+        <v>0.8052277589194365</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.72970221003054</v>
+        <v>10.26319341829008</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1705120521301791</v>
+        <v>0.1701271781620246</v>
       </c>
       <c r="C25">
-        <v>333.393058253224</v>
+        <v>331.129468641867</v>
       </c>
       <c r="D25">
-        <v>410.0620582532241</v>
+        <v>411.3314686418671</v>
       </c>
       <c r="E25">
-        <v>-0.7409999999999997</v>
+        <v>2.792000000000016</v>
       </c>
       <c r="F25">
-        <v>81.259</v>
+        <v>84.79200000000002</v>
       </c>
       <c r="G25">
         <v>4.59</v>
@@ -3337,28 +3337,28 @@
         <v>43.2</v>
       </c>
       <c r="M25">
-        <v>4.2092162</v>
+        <v>4.392225600000001</v>
       </c>
       <c r="N25">
-        <v>38.9907838</v>
+        <v>38.80777439999999</v>
       </c>
       <c r="O25">
-        <v>9.357788111999998</v>
+        <v>9.313865855999998</v>
       </c>
       <c r="P25">
-        <v>29.632995688</v>
+        <v>29.49390854399999</v>
       </c>
       <c r="Q25">
-        <v>38.43299568800001</v>
+        <v>38.293908544</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2096849508184144</v>
+        <v>0.2114195502131902</v>
       </c>
       <c r="T25">
-        <v>0.8052277589194365</v>
+        <v>0.8137504913381434</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.26319341829008</v>
+        <v>9.835560359194661</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1701271781620246</v>
+        <v>0.17006530419387</v>
       </c>
       <c r="C26">
-        <v>331.1294686418671</v>
+        <v>327.8012781046277</v>
       </c>
       <c r="D26">
-        <v>411.3314686418671</v>
+        <v>411.5362781046277</v>
       </c>
       <c r="E26">
-        <v>2.792000000000002</v>
+        <v>6.325000000000003</v>
       </c>
       <c r="F26">
-        <v>84.792</v>
+        <v>88.325</v>
       </c>
       <c r="G26">
         <v>4.59</v>
@@ -3419,45 +3419,45 @@
         <v>43.2</v>
       </c>
       <c r="M26">
-        <v>4.3922256</v>
+        <v>4.7253875</v>
       </c>
       <c r="N26">
-        <v>38.8077744</v>
+        <v>38.47461249999999</v>
       </c>
       <c r="O26">
-        <v>9.313865856</v>
+        <v>9.233906999999999</v>
       </c>
       <c r="P26">
-        <v>29.493908544</v>
+        <v>29.24070549999999</v>
       </c>
       <c r="Q26">
-        <v>38.293908544</v>
+        <v>38.0407055</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2114195502131902</v>
+        <v>0.2132004055918266</v>
       </c>
       <c r="T26">
-        <v>0.8137504913381434</v>
+        <v>0.8225004966213493</v>
       </c>
       <c r="U26">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V26">
         <v>0.24</v>
       </c>
       <c r="W26">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>9.835560359194664</v>
+        <v>9.142107393309013</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.17006530419387</v>
+        <v>0.1696933502257154</v>
       </c>
       <c r="C27">
-        <v>327.8012781046277</v>
+        <v>325.503796810044</v>
       </c>
       <c r="D27">
-        <v>411.5362781046277</v>
+        <v>412.7717968100441</v>
       </c>
       <c r="E27">
-        <v>6.325000000000003</v>
+        <v>9.858000000000004</v>
       </c>
       <c r="F27">
-        <v>88.325</v>
+        <v>91.858</v>
       </c>
       <c r="G27">
         <v>4.59</v>
@@ -3501,28 +3501,28 @@
         <v>43.2</v>
       </c>
       <c r="M27">
-        <v>4.7253875</v>
+        <v>4.914403</v>
       </c>
       <c r="N27">
-        <v>38.47461249999999</v>
+        <v>38.285597</v>
       </c>
       <c r="O27">
-        <v>9.233906999999999</v>
+        <v>9.188543279999999</v>
       </c>
       <c r="P27">
-        <v>29.24070549999999</v>
+        <v>29.09705372</v>
       </c>
       <c r="Q27">
-        <v>38.0407055</v>
+        <v>37.89705372</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2132004055918266</v>
+        <v>0.2150293921969127</v>
       </c>
       <c r="T27">
-        <v>0.8225004966213493</v>
+        <v>0.8314869885338309</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.142107393309013</v>
+        <v>8.790487878181743</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1696933502257154</v>
+        <v>0.1693213962575608</v>
       </c>
       <c r="C28">
-        <v>325.503796810044</v>
+        <v>323.2137564301382</v>
       </c>
       <c r="D28">
-        <v>412.7717968100441</v>
+        <v>414.0147564301382</v>
       </c>
       <c r="E28">
-        <v>9.858000000000004</v>
+        <v>13.39100000000001</v>
       </c>
       <c r="F28">
-        <v>91.858</v>
+        <v>95.39100000000001</v>
       </c>
       <c r="G28">
         <v>4.59</v>
@@ -3583,28 +3583,28 @@
         <v>43.2</v>
       </c>
       <c r="M28">
-        <v>4.914403</v>
+        <v>5.1034185</v>
       </c>
       <c r="N28">
-        <v>38.285597</v>
+        <v>38.0965815</v>
       </c>
       <c r="O28">
-        <v>9.188543279999999</v>
+        <v>9.14317956</v>
       </c>
       <c r="P28">
-        <v>29.09705372</v>
+        <v>28.95340194</v>
       </c>
       <c r="Q28">
-        <v>37.89705372</v>
+        <v>37.75340194</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2150293921969127</v>
+        <v>0.2169084880240559</v>
       </c>
       <c r="T28">
-        <v>0.8314869885338309</v>
+        <v>0.8407196857041888</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.790487878181743</v>
+        <v>8.464914253063903</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1693213962575608</v>
+        <v>0.1689494422894063</v>
       </c>
       <c r="C29">
-        <v>323.2137564301382</v>
+        <v>320.9312243873281</v>
       </c>
       <c r="D29">
-        <v>414.0147564301382</v>
+        <v>415.2652243873282</v>
       </c>
       <c r="E29">
-        <v>13.39100000000001</v>
+        <v>16.92400000000001</v>
       </c>
       <c r="F29">
-        <v>95.39100000000001</v>
+        <v>98.92400000000001</v>
       </c>
       <c r="G29">
         <v>4.59</v>
@@ -3665,28 +3665,28 @@
         <v>43.2</v>
       </c>
       <c r="M29">
-        <v>5.1034185</v>
+        <v>5.292434</v>
       </c>
       <c r="N29">
-        <v>38.0965815</v>
+        <v>37.907566</v>
       </c>
       <c r="O29">
-        <v>9.14317956</v>
+        <v>9.097815839999999</v>
       </c>
       <c r="P29">
-        <v>28.95340194</v>
+        <v>28.80975016</v>
       </c>
       <c r="Q29">
-        <v>37.75340194</v>
+        <v>37.60975016</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2169084880240559</v>
+        <v>0.2188397809575087</v>
       </c>
       <c r="T29">
-        <v>0.8407196857041888</v>
+        <v>0.8502088466848344</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.464914253063903</v>
+        <v>8.162595886883047</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1689494422894063</v>
+        <v>0.1685774883212517</v>
       </c>
       <c r="C30">
-        <v>320.9312243873281</v>
+        <v>318.6562689210565</v>
       </c>
       <c r="D30">
-        <v>415.2652243873282</v>
+        <v>416.5232689210566</v>
       </c>
       <c r="E30">
-        <v>16.92400000000001</v>
+        <v>20.45700000000002</v>
       </c>
       <c r="F30">
-        <v>98.92400000000001</v>
+        <v>102.457</v>
       </c>
       <c r="G30">
         <v>4.59</v>
@@ -3747,28 +3747,28 @@
         <v>43.2</v>
       </c>
       <c r="M30">
-        <v>5.292434</v>
+        <v>5.481449500000001</v>
       </c>
       <c r="N30">
-        <v>37.907566</v>
+        <v>37.71855049999999</v>
       </c>
       <c r="O30">
-        <v>9.097815839999999</v>
+        <v>9.052452119999998</v>
       </c>
       <c r="P30">
-        <v>28.80975016</v>
+        <v>28.66609837999999</v>
       </c>
       <c r="Q30">
-        <v>37.60975016</v>
+        <v>37.46609838</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2188397809575087</v>
+        <v>0.2208254765088053</v>
       </c>
       <c r="T30">
-        <v>0.8502088466848344</v>
+        <v>0.8599653079747941</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.162595886883047</v>
+        <v>7.881127063197424</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1685774883212517</v>
+        <v>0.1682055343530972</v>
       </c>
       <c r="C31">
-        <v>318.6562689210566</v>
+        <v>316.3889591002032</v>
       </c>
       <c r="D31">
-        <v>416.5232689210566</v>
+        <v>417.7889591002032</v>
       </c>
       <c r="E31">
-        <v>20.45699999999999</v>
+        <v>23.98999999999999</v>
       </c>
       <c r="F31">
-        <v>102.457</v>
+        <v>105.99</v>
       </c>
       <c r="G31">
         <v>4.59</v>
@@ -3829,28 +3829,28 @@
         <v>43.2</v>
       </c>
       <c r="M31">
-        <v>5.481449499999999</v>
+        <v>5.670464999999999</v>
       </c>
       <c r="N31">
-        <v>37.7185505</v>
+        <v>37.529535</v>
       </c>
       <c r="O31">
-        <v>9.05245212</v>
+        <v>9.007088399999999</v>
       </c>
       <c r="P31">
-        <v>28.66609838</v>
+        <v>28.52244659999999</v>
       </c>
       <c r="Q31">
-        <v>37.46609838000001</v>
+        <v>37.3224466</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2208254765088053</v>
+        <v>0.2228679062187102</v>
       </c>
       <c r="T31">
-        <v>0.8599653079747941</v>
+        <v>0.8700005253016095</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.881127063197427</v>
+        <v>7.618422827757512</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1682055343530972</v>
+        <v>0.1680220603849426</v>
       </c>
       <c r="C32">
-        <v>316.3889591002032</v>
+        <v>313.4831240975519</v>
       </c>
       <c r="D32">
-        <v>417.7889591002032</v>
+        <v>418.4161240975519</v>
       </c>
       <c r="E32">
-        <v>23.98999999999999</v>
+        <v>27.523</v>
       </c>
       <c r="F32">
-        <v>105.99</v>
+        <v>109.523</v>
       </c>
       <c r="G32">
         <v>4.59</v>
@@ -3911,45 +3911,45 @@
         <v>43.2</v>
       </c>
       <c r="M32">
-        <v>5.670464999999999</v>
+        <v>5.9470989</v>
       </c>
       <c r="N32">
-        <v>37.529535</v>
+        <v>37.2529011</v>
       </c>
       <c r="O32">
-        <v>9.007088399999999</v>
+        <v>8.940696263999998</v>
       </c>
       <c r="P32">
-        <v>28.52244659999999</v>
+        <v>28.312204836</v>
       </c>
       <c r="Q32">
-        <v>37.3224466</v>
+        <v>37.112204836</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2228679062187102</v>
+        <v>0.2249695367897719</v>
       </c>
       <c r="T32">
-        <v>0.8700005253016095</v>
+        <v>0.8803266184929704</v>
       </c>
       <c r="U32">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V32">
         <v>0.24</v>
       </c>
       <c r="W32">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>7.618422827757512</v>
+        <v>7.264046004010458</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1680220603849426</v>
+        <v>0.1676561864167881</v>
       </c>
       <c r="C33">
-        <v>313.4831240975519</v>
+        <v>311.2064211487316</v>
       </c>
       <c r="D33">
-        <v>418.4161240975519</v>
+        <v>419.6724211487316</v>
       </c>
       <c r="E33">
-        <v>27.523</v>
+        <v>31.05600000000001</v>
       </c>
       <c r="F33">
-        <v>109.523</v>
+        <v>113.056</v>
       </c>
       <c r="G33">
         <v>4.59</v>
@@ -3993,28 +3993,28 @@
         <v>43.2</v>
       </c>
       <c r="M33">
-        <v>5.9470989</v>
+        <v>6.1389408</v>
       </c>
       <c r="N33">
-        <v>37.2529011</v>
+        <v>37.0610592</v>
       </c>
       <c r="O33">
-        <v>8.940696263999998</v>
+        <v>8.894654207999999</v>
       </c>
       <c r="P33">
-        <v>28.312204836</v>
+        <v>28.166404992</v>
       </c>
       <c r="Q33">
-        <v>37.112204836</v>
+        <v>36.966404992</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2249695367897719</v>
+        <v>0.2271329800246883</v>
       </c>
       <c r="T33">
-        <v>0.8803266184929704</v>
+        <v>0.8909564203076068</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.264046004010458</v>
+        <v>7.037044566385132</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1676561864167881</v>
+        <v>0.1672903124486335</v>
       </c>
       <c r="C34">
-        <v>311.2064211487316</v>
+        <v>308.9372849989101</v>
       </c>
       <c r="D34">
-        <v>419.6724211487316</v>
+        <v>420.9362849989101</v>
       </c>
       <c r="E34">
-        <v>31.05600000000001</v>
+        <v>34.58900000000001</v>
       </c>
       <c r="F34">
-        <v>113.056</v>
+        <v>116.589</v>
       </c>
       <c r="G34">
         <v>4.59</v>
@@ -4075,28 +4075,28 @@
         <v>43.2</v>
       </c>
       <c r="M34">
-        <v>6.1389408</v>
+        <v>6.330782700000001</v>
       </c>
       <c r="N34">
-        <v>37.0610592</v>
+        <v>36.8692173</v>
       </c>
       <c r="O34">
-        <v>8.894654207999999</v>
+        <v>8.848612151999999</v>
       </c>
       <c r="P34">
-        <v>28.166404992</v>
+        <v>28.02060514799999</v>
       </c>
       <c r="Q34">
-        <v>36.966404992</v>
+        <v>36.820605148</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2271329800246883</v>
+        <v>0.2293610036546768</v>
       </c>
       <c r="T34">
-        <v>0.8909564203076068</v>
+        <v>0.9019035296390978</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.037044566385132</v>
+        <v>6.823800791646187</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1672903124486335</v>
+        <v>0.1669244384804789</v>
       </c>
       <c r="C35">
-        <v>308.9372849989101</v>
+        <v>306.6757842179353</v>
       </c>
       <c r="D35">
-        <v>420.9362849989101</v>
+        <v>422.2077842179353</v>
       </c>
       <c r="E35">
-        <v>34.58900000000001</v>
+        <v>38.12200000000001</v>
       </c>
       <c r="F35">
-        <v>116.589</v>
+        <v>120.122</v>
       </c>
       <c r="G35">
         <v>4.59</v>
@@ -4157,28 +4157,28 @@
         <v>43.2</v>
       </c>
       <c r="M35">
-        <v>6.330782700000001</v>
+        <v>6.522624600000001</v>
       </c>
       <c r="N35">
-        <v>36.8692173</v>
+        <v>36.6773754</v>
       </c>
       <c r="O35">
-        <v>8.848612151999999</v>
+        <v>8.802570095999998</v>
       </c>
       <c r="P35">
-        <v>28.02060514799999</v>
+        <v>27.874805304</v>
       </c>
       <c r="Q35">
-        <v>36.820605148</v>
+        <v>36.674805304</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2293610036546768</v>
+        <v>0.2316565431522408</v>
       </c>
       <c r="T35">
-        <v>0.9019035296390978</v>
+        <v>0.9131823695563916</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.823800791646187</v>
+        <v>6.623100768362476</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1669244384804789</v>
+        <v>0.1665585645123243</v>
       </c>
       <c r="C36">
-        <v>306.6757842179353</v>
+        <v>304.421988206666</v>
       </c>
       <c r="D36">
-        <v>422.2077842179353</v>
+        <v>423.4869882066661</v>
       </c>
       <c r="E36">
-        <v>38.12200000000001</v>
+        <v>41.65500000000002</v>
       </c>
       <c r="F36">
-        <v>120.122</v>
+        <v>123.655</v>
       </c>
       <c r="G36">
         <v>4.59</v>
@@ -4239,28 +4239,28 @@
         <v>43.2</v>
       </c>
       <c r="M36">
-        <v>6.522624600000001</v>
+        <v>6.714466500000001</v>
       </c>
       <c r="N36">
-        <v>36.6773754</v>
+        <v>36.4855335</v>
       </c>
       <c r="O36">
-        <v>8.802570095999998</v>
+        <v>8.756528039999999</v>
       </c>
       <c r="P36">
-        <v>27.874805304</v>
+        <v>27.72900546</v>
       </c>
       <c r="Q36">
-        <v>36.674805304</v>
+        <v>36.52900546</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2316565431522408</v>
+        <v>0.2340227146343452</v>
       </c>
       <c r="T36">
-        <v>0.9131823695563916</v>
+        <v>0.92480825070191</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.623100768362476</v>
+        <v>6.433869317837834</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1665585645123243</v>
+        <v>0.1661926905441698</v>
       </c>
       <c r="C37">
-        <v>304.421988206666</v>
+        <v>302.1759672095993</v>
       </c>
       <c r="D37">
-        <v>423.4869882066661</v>
+        <v>424.7739672095993</v>
       </c>
       <c r="E37">
-        <v>41.65500000000002</v>
+        <v>45.18800000000002</v>
       </c>
       <c r="F37">
-        <v>123.655</v>
+        <v>127.188</v>
       </c>
       <c r="G37">
         <v>4.59</v>
@@ -4321,28 +4321,28 @@
         <v>43.2</v>
       </c>
       <c r="M37">
-        <v>6.714466500000001</v>
+        <v>6.906308400000001</v>
       </c>
       <c r="N37">
-        <v>36.4855335</v>
+        <v>36.2936916</v>
       </c>
       <c r="O37">
-        <v>8.756528039999999</v>
+        <v>8.710485983999998</v>
       </c>
       <c r="P37">
-        <v>27.72900546</v>
+        <v>27.583205616</v>
       </c>
       <c r="Q37">
-        <v>36.52900546</v>
+        <v>36.383205616</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2340227146343452</v>
+        <v>0.2364628289752653</v>
       </c>
       <c r="T37">
-        <v>0.92480825070191</v>
+        <v>0.9367974406332257</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.433869317837834</v>
+        <v>6.255150725675672</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1661926905441698</v>
+        <v>0.1661080165760153</v>
       </c>
       <c r="C38">
-        <v>302.1759672095993</v>
+        <v>298.9419273154678</v>
       </c>
       <c r="D38">
-        <v>424.7739672095993</v>
+        <v>425.0729273154678</v>
       </c>
       <c r="E38">
-        <v>45.188</v>
+        <v>48.721</v>
       </c>
       <c r="F38">
-        <v>127.188</v>
+        <v>130.721</v>
       </c>
       <c r="G38">
         <v>4.59</v>
@@ -4403,45 +4403,45 @@
         <v>43.2</v>
       </c>
       <c r="M38">
-        <v>6.9063084</v>
+        <v>7.228871300000001</v>
       </c>
       <c r="N38">
-        <v>36.2936916</v>
+        <v>35.97112869999999</v>
       </c>
       <c r="O38">
-        <v>8.710485983999998</v>
+        <v>8.633070887999999</v>
       </c>
       <c r="P38">
-        <v>27.583205616</v>
+        <v>27.338057812</v>
       </c>
       <c r="Q38">
-        <v>36.383205616</v>
+        <v>36.138057812</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2364628289752653</v>
+        <v>0.2389804072635162</v>
       </c>
       <c r="T38">
-        <v>0.9367974406332256</v>
+        <v>0.94916723976871</v>
       </c>
       <c r="U38">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V38">
         <v>0.24</v>
       </c>
       <c r="W38">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>6.255150725675673</v>
+        <v>5.976036673941061</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1661080165760153</v>
+        <v>0.1657497426078607</v>
       </c>
       <c r="C39">
-        <v>298.9419273154678</v>
+        <v>296.6785637574755</v>
       </c>
       <c r="D39">
-        <v>425.0729273154678</v>
+        <v>426.3425637574755</v>
       </c>
       <c r="E39">
-        <v>48.721</v>
+        <v>52.25400000000002</v>
       </c>
       <c r="F39">
-        <v>130.721</v>
+        <v>134.254</v>
       </c>
       <c r="G39">
         <v>4.59</v>
@@ -4485,28 +4485,28 @@
         <v>43.2</v>
       </c>
       <c r="M39">
-        <v>7.228871300000001</v>
+        <v>7.424246200000002</v>
       </c>
       <c r="N39">
-        <v>35.97112869999999</v>
+        <v>35.7757538</v>
       </c>
       <c r="O39">
-        <v>8.633070887999999</v>
+        <v>8.586180912</v>
       </c>
       <c r="P39">
-        <v>27.338057812</v>
+        <v>27.189572888</v>
       </c>
       <c r="Q39">
-        <v>36.138057812</v>
+        <v>35.989572888</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2389804072635162</v>
+        <v>0.241579197754614</v>
       </c>
       <c r="T39">
-        <v>0.94916723976871</v>
+        <v>0.9619360646827585</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.976036673941061</v>
+        <v>5.818772550942612</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1657497426078607</v>
+        <v>0.1653914686397061</v>
       </c>
       <c r="C40">
-        <v>296.6785637574755</v>
+        <v>294.4228073923938</v>
       </c>
       <c r="D40">
-        <v>426.3425637574755</v>
+        <v>427.6198073923938</v>
       </c>
       <c r="E40">
-        <v>52.25400000000002</v>
+        <v>55.78700000000001</v>
       </c>
       <c r="F40">
-        <v>134.254</v>
+        <v>137.787</v>
       </c>
       <c r="G40">
         <v>4.59</v>
@@ -4567,28 +4567,28 @@
         <v>43.2</v>
       </c>
       <c r="M40">
-        <v>7.424246200000002</v>
+        <v>7.619621100000001</v>
       </c>
       <c r="N40">
-        <v>35.7757538</v>
+        <v>35.58037889999999</v>
       </c>
       <c r="O40">
-        <v>8.586180912</v>
+        <v>8.539290935999999</v>
       </c>
       <c r="P40">
-        <v>27.189572888</v>
+        <v>27.04108796399999</v>
       </c>
       <c r="Q40">
-        <v>35.989572888</v>
+        <v>35.841087964</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.241579197754614</v>
+        <v>0.2442631944913215</v>
       </c>
       <c r="T40">
-        <v>0.9619360646827585</v>
+        <v>0.9751235395939889</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.818772550942612</v>
+        <v>5.669573254764596</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1653914686397061</v>
+        <v>0.1650331946715516</v>
       </c>
       <c r="C41">
-        <v>294.4228073923938</v>
+        <v>292.1747267948973</v>
       </c>
       <c r="D41">
-        <v>427.6198073923938</v>
+        <v>428.9047267948973</v>
       </c>
       <c r="E41">
-        <v>55.78700000000001</v>
+        <v>59.32000000000002</v>
       </c>
       <c r="F41">
-        <v>137.787</v>
+        <v>141.32</v>
       </c>
       <c r="G41">
         <v>4.59</v>
@@ -4649,28 +4649,28 @@
         <v>43.2</v>
       </c>
       <c r="M41">
-        <v>7.619621100000001</v>
+        <v>7.814996000000002</v>
       </c>
       <c r="N41">
-        <v>35.58037889999999</v>
+        <v>35.385004</v>
       </c>
       <c r="O41">
-        <v>8.539290935999999</v>
+        <v>8.492400959999998</v>
       </c>
       <c r="P41">
-        <v>27.04108796399999</v>
+        <v>26.89260304</v>
       </c>
       <c r="Q41">
-        <v>35.841087964</v>
+        <v>35.69260304</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2442631944913215</v>
+        <v>0.2470366577859193</v>
       </c>
       <c r="T41">
-        <v>0.9751235395939889</v>
+        <v>0.9887505970022604</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.669573254764596</v>
+        <v>5.52783392339548</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1650331946715516</v>
+        <v>0.164674920703397</v>
       </c>
       <c r="C42">
-        <v>292.1747267948973</v>
+        <v>289.9343913663629</v>
       </c>
       <c r="D42">
-        <v>428.9047267948973</v>
+        <v>430.1973913663629</v>
       </c>
       <c r="E42">
-        <v>59.32000000000002</v>
+        <v>62.85300000000001</v>
       </c>
       <c r="F42">
-        <v>141.32</v>
+        <v>144.853</v>
       </c>
       <c r="G42">
         <v>4.59</v>
@@ -4731,28 +4731,28 @@
         <v>43.2</v>
       </c>
       <c r="M42">
-        <v>7.814996000000002</v>
+        <v>8.010370900000002</v>
       </c>
       <c r="N42">
-        <v>35.385004</v>
+        <v>35.18962909999999</v>
       </c>
       <c r="O42">
-        <v>8.492400959999998</v>
+        <v>8.445510983999997</v>
       </c>
       <c r="P42">
-        <v>26.89260304</v>
+        <v>26.744118116</v>
       </c>
       <c r="Q42">
-        <v>35.69260304</v>
+        <v>35.544118116</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2470366577859193</v>
+        <v>0.2499041367854186</v>
       </c>
       <c r="T42">
-        <v>0.9887505970022604</v>
+        <v>1.002839588559965</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.52783392339548</v>
+        <v>5.393008705751688</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.164674920703397</v>
+        <v>0.1643166467352424</v>
       </c>
       <c r="C43">
-        <v>289.9343913663629</v>
+        <v>287.701871347364</v>
       </c>
       <c r="D43">
-        <v>430.1973913663629</v>
+        <v>431.497871347364</v>
       </c>
       <c r="E43">
-        <v>62.85300000000001</v>
+        <v>66.38600000000002</v>
       </c>
       <c r="F43">
-        <v>144.853</v>
+        <v>148.386</v>
       </c>
       <c r="G43">
         <v>4.59</v>
@@ -4813,28 +4813,28 @@
         <v>43.2</v>
       </c>
       <c r="M43">
-        <v>8.010370900000002</v>
+        <v>8.205745800000001</v>
       </c>
       <c r="N43">
-        <v>35.18962909999999</v>
+        <v>34.99425419999999</v>
       </c>
       <c r="O43">
-        <v>8.445510983999997</v>
+        <v>8.398621007999997</v>
       </c>
       <c r="P43">
-        <v>26.744118116</v>
+        <v>26.59563319199999</v>
       </c>
       <c r="Q43">
-        <v>35.544118116</v>
+        <v>35.395633192</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2499041367854186</v>
+        <v>0.2528704943711076</v>
       </c>
       <c r="T43">
-        <v>1.002839588559965</v>
+        <v>1.017414407412762</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.393008705751688</v>
+        <v>5.264603736567125</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1643166467352424</v>
+        <v>0.1639583727670879</v>
       </c>
       <c r="C44">
-        <v>287.701871347364</v>
+        <v>285.4772378303943</v>
       </c>
       <c r="D44">
-        <v>431.497871347364</v>
+        <v>432.8062378303943</v>
       </c>
       <c r="E44">
-        <v>66.386</v>
+        <v>69.91900000000001</v>
       </c>
       <c r="F44">
-        <v>148.386</v>
+        <v>151.919</v>
       </c>
       <c r="G44">
         <v>4.59</v>
@@ -4895,28 +4895,28 @@
         <v>43.2</v>
       </c>
       <c r="M44">
-        <v>8.205745800000001</v>
+        <v>8.401120700000002</v>
       </c>
       <c r="N44">
-        <v>34.99425419999999</v>
+        <v>34.7988793</v>
       </c>
       <c r="O44">
-        <v>8.398621007999997</v>
+        <v>8.351731031999998</v>
       </c>
       <c r="P44">
-        <v>26.59563319199999</v>
+        <v>26.447148268</v>
       </c>
       <c r="Q44">
-        <v>35.395633192</v>
+        <v>35.247148268</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2528704943711076</v>
+        <v>0.2559409346791015</v>
       </c>
       <c r="T44">
-        <v>1.017414407412762</v>
+        <v>1.032500623418289</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.264603736567125</v>
+        <v>5.14217109153068</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1639583727670879</v>
+        <v>0.1636000987989333</v>
       </c>
       <c r="C45">
-        <v>285.4772378303943</v>
+        <v>283.2605627728225</v>
       </c>
       <c r="D45">
-        <v>432.8062378303943</v>
+        <v>434.1225627728225</v>
       </c>
       <c r="E45">
-        <v>69.91900000000001</v>
+        <v>73.452</v>
       </c>
       <c r="F45">
-        <v>151.919</v>
+        <v>155.452</v>
       </c>
       <c r="G45">
         <v>4.59</v>
@@ -4977,28 +4977,28 @@
         <v>43.2</v>
       </c>
       <c r="M45">
-        <v>8.401120700000002</v>
+        <v>8.596495600000001</v>
       </c>
       <c r="N45">
-        <v>34.7988793</v>
+        <v>34.60350439999999</v>
       </c>
       <c r="O45">
-        <v>8.351731031999998</v>
+        <v>8.304841055999997</v>
       </c>
       <c r="P45">
-        <v>26.447148268</v>
+        <v>26.29866334399999</v>
       </c>
       <c r="Q45">
-        <v>35.247148268</v>
+        <v>35.098663344</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2559409346791015</v>
+        <v>0.2591210335695238</v>
       </c>
       <c r="T45">
-        <v>1.032500623418289</v>
+        <v>1.048125632852586</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.14217109153068</v>
+        <v>5.025303566723164</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1636000987989333</v>
+        <v>0.1632418248307788</v>
       </c>
       <c r="C46">
-        <v>283.2605627728225</v>
+        <v>281.0519190100842</v>
       </c>
       <c r="D46">
-        <v>434.1225627728225</v>
+        <v>435.4469190100843</v>
       </c>
       <c r="E46">
-        <v>73.452</v>
+        <v>76.98500000000001</v>
       </c>
       <c r="F46">
-        <v>155.452</v>
+        <v>158.985</v>
       </c>
       <c r="G46">
         <v>4.59</v>
@@ -5059,28 +5059,28 @@
         <v>43.2</v>
       </c>
       <c r="M46">
-        <v>8.596495600000001</v>
+        <v>8.791870500000002</v>
       </c>
       <c r="N46">
-        <v>34.60350439999999</v>
+        <v>34.40812949999999</v>
       </c>
       <c r="O46">
-        <v>8.304841055999997</v>
+        <v>8.257951079999998</v>
       </c>
       <c r="P46">
-        <v>26.29866334399999</v>
+        <v>26.15017842</v>
       </c>
       <c r="Q46">
-        <v>35.098663344</v>
+        <v>34.95017842</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2591210335695238</v>
+        <v>0.2624167724195977</v>
       </c>
       <c r="T46">
-        <v>1.048125632852586</v>
+        <v>1.064318824448129</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.025303566723164</v>
+        <v>4.913630154129316</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1632418248307788</v>
+        <v>0.1628835508626242</v>
       </c>
       <c r="C47">
-        <v>281.0519190100842</v>
+        <v>278.8513802691169</v>
       </c>
       <c r="D47">
-        <v>435.4469190100843</v>
+        <v>436.779380269117</v>
       </c>
       <c r="E47">
-        <v>76.98500000000001</v>
+        <v>80.518</v>
       </c>
       <c r="F47">
-        <v>158.985</v>
+        <v>162.518</v>
       </c>
       <c r="G47">
         <v>4.59</v>
@@ -5141,28 +5141,28 @@
         <v>43.2</v>
       </c>
       <c r="M47">
-        <v>8.791870500000002</v>
+        <v>8.987245400000001</v>
       </c>
       <c r="N47">
-        <v>34.40812949999999</v>
+        <v>34.2127546</v>
       </c>
       <c r="O47">
-        <v>8.257951079999998</v>
+        <v>8.211061103999999</v>
       </c>
       <c r="P47">
-        <v>26.15017842</v>
+        <v>26.001693496</v>
       </c>
       <c r="Q47">
-        <v>34.95017842</v>
+        <v>34.801693496</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2624167724195977</v>
+        <v>0.2658345756715262</v>
       </c>
       <c r="T47">
-        <v>1.064318824448129</v>
+        <v>1.081111763880544</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.913630154129316</v>
+        <v>4.806812107300418</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1628835508626242</v>
+        <v>0.1625252768944696</v>
       </c>
       <c r="C48">
-        <v>278.8513802691169</v>
+        <v>276.659021182041</v>
       </c>
       <c r="D48">
-        <v>436.779380269117</v>
+        <v>438.120021182041</v>
       </c>
       <c r="E48">
-        <v>80.518</v>
+        <v>84.05100000000002</v>
       </c>
       <c r="F48">
-        <v>162.518</v>
+        <v>166.051</v>
       </c>
       <c r="G48">
         <v>4.59</v>
@@ -5223,28 +5223,28 @@
         <v>43.2</v>
       </c>
       <c r="M48">
-        <v>8.987245400000001</v>
+        <v>9.182620300000002</v>
       </c>
       <c r="N48">
-        <v>34.2127546</v>
+        <v>34.01737969999999</v>
       </c>
       <c r="O48">
-        <v>8.211061103999999</v>
+        <v>8.164171127999998</v>
       </c>
       <c r="P48">
-        <v>26.001693496</v>
+        <v>25.85320857199999</v>
       </c>
       <c r="Q48">
-        <v>34.801693496</v>
+        <v>34.653208572</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2658345756715262</v>
+        <v>0.2693813526310747</v>
       </c>
       <c r="T48">
-        <v>1.081111763880544</v>
+        <v>1.098538399140598</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.806812107300418</v>
+        <v>4.704539509272749</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1625252768944696</v>
+        <v>0.1621670029263151</v>
       </c>
       <c r="C49">
-        <v>276.659021182041</v>
+        <v>274.4749173000946</v>
       </c>
       <c r="D49">
-        <v>438.120021182041</v>
+        <v>439.4689173000946</v>
       </c>
       <c r="E49">
-        <v>84.05100000000002</v>
+        <v>87.58400000000003</v>
       </c>
       <c r="F49">
-        <v>166.051</v>
+        <v>169.584</v>
       </c>
       <c r="G49">
         <v>4.59</v>
@@ -5305,28 +5305,28 @@
         <v>43.2</v>
       </c>
       <c r="M49">
-        <v>9.182620300000002</v>
+        <v>9.377995200000003</v>
       </c>
       <c r="N49">
-        <v>34.01737969999999</v>
+        <v>33.82200479999999</v>
       </c>
       <c r="O49">
-        <v>8.164171127999998</v>
+        <v>8.117281151999999</v>
       </c>
       <c r="P49">
-        <v>25.85320857199999</v>
+        <v>25.704723648</v>
       </c>
       <c r="Q49">
-        <v>34.653208572</v>
+        <v>34.504723648</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2693813526310747</v>
+        <v>0.2730645440890674</v>
       </c>
       <c r="T49">
-        <v>1.098538399140598</v>
+        <v>1.116635289602961</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.704539509272749</v>
+        <v>4.606528269496234</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.162167002926315</v>
+        <v>0.1618087289581605</v>
       </c>
       <c r="C50">
-        <v>274.4749173000947</v>
+        <v>272.2991451078271</v>
       </c>
       <c r="D50">
-        <v>439.4689173000947</v>
+        <v>440.8261451078271</v>
       </c>
       <c r="E50">
-        <v>87.584</v>
+        <v>91.11699999999999</v>
       </c>
       <c r="F50">
-        <v>169.584</v>
+        <v>173.117</v>
       </c>
       <c r="G50">
         <v>4.59</v>
@@ -5387,28 +5387,28 @@
         <v>43.2</v>
       </c>
       <c r="M50">
-        <v>9.377995200000001</v>
+        <v>9.5733701</v>
       </c>
       <c r="N50">
-        <v>33.82200479999999</v>
+        <v>33.6266299</v>
       </c>
       <c r="O50">
-        <v>8.117281151999999</v>
+        <v>8.070391175999999</v>
       </c>
       <c r="P50">
-        <v>25.704723648</v>
+        <v>25.556238724</v>
       </c>
       <c r="Q50">
-        <v>34.504723648</v>
+        <v>34.356238724</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2730645440890674</v>
+        <v>0.2768921744277656</v>
       </c>
       <c r="T50">
-        <v>1.116635289602961</v>
+        <v>1.13544186204424</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.606528269496234</v>
+        <v>4.512517488486107</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1618087289581605</v>
+        <v>0.1624004549900059</v>
       </c>
       <c r="C51">
-        <v>272.2991451078271</v>
+        <v>266.5290328632758</v>
       </c>
       <c r="D51">
-        <v>440.8261451078271</v>
+        <v>438.5890328632758</v>
       </c>
       <c r="E51">
-        <v>91.11699999999999</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="F51">
-        <v>173.117</v>
+        <v>176.65</v>
       </c>
       <c r="G51">
         <v>4.59</v>
@@ -5469,45 +5469,45 @@
         <v>43.2</v>
       </c>
       <c r="M51">
-        <v>9.5733701</v>
+        <v>10.21037</v>
       </c>
       <c r="N51">
-        <v>33.6266299</v>
+        <v>32.98962999999999</v>
       </c>
       <c r="O51">
-        <v>8.070391175999999</v>
+        <v>7.917511199999997</v>
       </c>
       <c r="P51">
-        <v>25.556238724</v>
+        <v>25.07211879999999</v>
       </c>
       <c r="Q51">
-        <v>34.356238724</v>
+        <v>33.8721188</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2768921744277656</v>
+        <v>0.2808729099800119</v>
       </c>
       <c r="T51">
-        <v>1.13544186204424</v>
+        <v>1.155000697383171</v>
       </c>
       <c r="U51">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V51">
         <v>0.24</v>
       </c>
       <c r="W51">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.512517488486107</v>
+        <v>4.230992608495088</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1624004549900059</v>
+        <v>0.1620611810218514</v>
       </c>
       <c r="C52">
-        <v>266.5290328632758</v>
+        <v>264.275925603576</v>
       </c>
       <c r="D52">
-        <v>438.5890328632758</v>
+        <v>439.868925603576</v>
       </c>
       <c r="E52">
-        <v>94.65000000000001</v>
+        <v>98.18300000000002</v>
       </c>
       <c r="F52">
-        <v>176.65</v>
+        <v>180.183</v>
       </c>
       <c r="G52">
         <v>4.59</v>
@@ -5551,28 +5551,28 @@
         <v>43.2</v>
       </c>
       <c r="M52">
-        <v>10.21037</v>
+        <v>10.4145774</v>
       </c>
       <c r="N52">
-        <v>32.98962999999999</v>
+        <v>32.78542259999999</v>
       </c>
       <c r="O52">
-        <v>7.917511199999997</v>
+        <v>7.868501423999997</v>
       </c>
       <c r="P52">
-        <v>25.07211879999999</v>
+        <v>24.91692117599999</v>
       </c>
       <c r="Q52">
-        <v>33.8721188</v>
+        <v>33.716921176</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2808729099800119</v>
+        <v>0.2850161245343906</v>
       </c>
       <c r="T52">
-        <v>1.155000697383171</v>
+        <v>1.175357852531854</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.230992608495088</v>
+        <v>4.14803196911283</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1620611810218514</v>
+        <v>0.1617219070536968</v>
       </c>
       <c r="C53">
-        <v>264.275925603576</v>
+        <v>262.0303101855798</v>
       </c>
       <c r="D53">
-        <v>439.868925603576</v>
+        <v>441.1563101855798</v>
       </c>
       <c r="E53">
-        <v>98.18300000000002</v>
+        <v>101.716</v>
       </c>
       <c r="F53">
-        <v>180.183</v>
+        <v>183.716</v>
       </c>
       <c r="G53">
         <v>4.59</v>
@@ -5633,28 +5633,28 @@
         <v>43.2</v>
       </c>
       <c r="M53">
-        <v>10.4145774</v>
+        <v>10.6187848</v>
       </c>
       <c r="N53">
-        <v>32.78542259999999</v>
+        <v>32.5812152</v>
       </c>
       <c r="O53">
-        <v>7.868501423999997</v>
+        <v>7.819491647999999</v>
       </c>
       <c r="P53">
-        <v>24.91692117599999</v>
+        <v>24.761723552</v>
       </c>
       <c r="Q53">
-        <v>33.716921176</v>
+        <v>33.561723552</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2850161245343906</v>
+        <v>0.289331973028535</v>
       </c>
       <c r="T53">
-        <v>1.175357852531854</v>
+        <v>1.196563222478399</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.14803196911283</v>
+        <v>4.068262123552969</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1617219070536968</v>
+        <v>0.1627924330855423</v>
       </c>
       <c r="C54">
-        <v>262.0303101855798</v>
+        <v>254.4605592461302</v>
       </c>
       <c r="D54">
-        <v>441.1563101855798</v>
+        <v>437.1195592461303</v>
       </c>
       <c r="E54">
-        <v>101.716</v>
+        <v>105.249</v>
       </c>
       <c r="F54">
-        <v>183.716</v>
+        <v>187.249</v>
       </c>
       <c r="G54">
         <v>4.59</v>
@@ -5715,45 +5715,45 @@
         <v>43.2</v>
       </c>
       <c r="M54">
-        <v>10.6187848</v>
+        <v>11.4783637</v>
       </c>
       <c r="N54">
-        <v>32.5812152</v>
+        <v>31.72163629999999</v>
       </c>
       <c r="O54">
-        <v>7.819491647999999</v>
+        <v>7.613192711999998</v>
       </c>
       <c r="P54">
-        <v>24.761723552</v>
+        <v>24.10844358799999</v>
       </c>
       <c r="Q54">
-        <v>33.561723552</v>
+        <v>32.908443588</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.289331973028535</v>
+        <v>0.2938314746500899</v>
       </c>
       <c r="T54">
-        <v>1.196563222478399</v>
+        <v>1.218670948592882</v>
       </c>
       <c r="U54">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V54">
         <v>0.24</v>
       </c>
       <c r="W54">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>4.068262123552969</v>
+        <v>3.763602646603713</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1627924330855423</v>
+        <v>0.1624797591173877</v>
       </c>
       <c r="C55">
-        <v>254.4605592461302</v>
+        <v>252.0989355686504</v>
       </c>
       <c r="D55">
-        <v>437.1195592461303</v>
+        <v>438.2909355686505</v>
       </c>
       <c r="E55">
-        <v>105.249</v>
+        <v>108.782</v>
       </c>
       <c r="F55">
-        <v>187.249</v>
+        <v>190.782</v>
       </c>
       <c r="G55">
         <v>4.59</v>
@@ -5797,28 +5797,28 @@
         <v>43.2</v>
       </c>
       <c r="M55">
-        <v>11.4783637</v>
+        <v>11.6949366</v>
       </c>
       <c r="N55">
-        <v>31.72163629999999</v>
+        <v>31.5050634</v>
       </c>
       <c r="O55">
-        <v>7.613192711999998</v>
+        <v>7.561215215999999</v>
       </c>
       <c r="P55">
-        <v>24.10844358799999</v>
+        <v>23.943848184</v>
       </c>
       <c r="Q55">
-        <v>32.908443588</v>
+        <v>32.743848184</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2938314746500899</v>
+        <v>0.2985266067769298</v>
       </c>
       <c r="T55">
-        <v>1.218670948592882</v>
+        <v>1.241739880190603</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.763602646603713</v>
+        <v>3.693906301296237</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1624797591173877</v>
+        <v>0.1621670851492331</v>
       </c>
       <c r="C56">
-        <v>252.0989355686504</v>
+        <v>249.7436067791537</v>
       </c>
       <c r="D56">
-        <v>438.2909355686505</v>
+        <v>439.4686067791537</v>
       </c>
       <c r="E56">
-        <v>108.782</v>
+        <v>112.315</v>
       </c>
       <c r="F56">
-        <v>190.782</v>
+        <v>194.315</v>
       </c>
       <c r="G56">
         <v>4.59</v>
@@ -5879,28 +5879,28 @@
         <v>43.2</v>
       </c>
       <c r="M56">
-        <v>11.6949366</v>
+        <v>11.9115095</v>
       </c>
       <c r="N56">
-        <v>31.5050634</v>
+        <v>31.28849049999999</v>
       </c>
       <c r="O56">
-        <v>7.561215215999999</v>
+        <v>7.509237719999998</v>
       </c>
       <c r="P56">
-        <v>23.943848184</v>
+        <v>23.77925278</v>
       </c>
       <c r="Q56">
-        <v>32.743848184</v>
+        <v>32.57925278</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2985266067769298</v>
+        <v>0.3034304114427403</v>
       </c>
       <c r="T56">
-        <v>1.241739880190603</v>
+        <v>1.265834097637112</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.693906301296237</v>
+        <v>3.626744368545396</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1621670851492331</v>
+        <v>0.1618544111810785</v>
       </c>
       <c r="C57">
-        <v>249.7436067791537</v>
+        <v>247.3946237567298</v>
       </c>
       <c r="D57">
-        <v>439.4686067791537</v>
+        <v>440.6526237567298</v>
       </c>
       <c r="E57">
-        <v>112.315</v>
+        <v>115.848</v>
       </c>
       <c r="F57">
-        <v>194.315</v>
+        <v>197.848</v>
       </c>
       <c r="G57">
         <v>4.59</v>
@@ -5961,28 +5961,28 @@
         <v>43.2</v>
       </c>
       <c r="M57">
-        <v>11.9115095</v>
+        <v>12.1280824</v>
       </c>
       <c r="N57">
-        <v>31.28849049999999</v>
+        <v>31.0719176</v>
       </c>
       <c r="O57">
-        <v>7.509237719999998</v>
+        <v>7.457260223999999</v>
       </c>
       <c r="P57">
-        <v>23.77925278</v>
+        <v>23.614657376</v>
       </c>
       <c r="Q57">
-        <v>32.57925278</v>
+        <v>32.414657376</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3034304114427403</v>
+        <v>0.3085571163206331</v>
       </c>
       <c r="T57">
-        <v>1.265834097637112</v>
+        <v>1.291023506785735</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.626744368545396</v>
+        <v>3.561981076249943</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1618544111810785</v>
+        <v>0.162754697212924</v>
       </c>
       <c r="C58">
-        <v>247.3946237567298</v>
+        <v>240.469597514791</v>
       </c>
       <c r="D58">
-        <v>440.6526237567298</v>
+        <v>437.2605975147911</v>
       </c>
       <c r="E58">
-        <v>115.848</v>
+        <v>119.381</v>
       </c>
       <c r="F58">
-        <v>197.848</v>
+        <v>201.381</v>
       </c>
       <c r="G58">
         <v>4.59</v>
@@ -6043,45 +6043,45 @@
         <v>43.2</v>
       </c>
       <c r="M58">
-        <v>12.1280824</v>
+        <v>12.9085221</v>
       </c>
       <c r="N58">
-        <v>31.0719176</v>
+        <v>30.29147789999999</v>
       </c>
       <c r="O58">
-        <v>7.457260223999999</v>
+        <v>7.269954695999998</v>
       </c>
       <c r="P58">
-        <v>23.614657376</v>
+        <v>23.02152320399999</v>
       </c>
       <c r="Q58">
-        <v>32.414657376</v>
+        <v>31.821523204</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3085571163206331</v>
+        <v>0.3139222725881954</v>
       </c>
       <c r="T58">
-        <v>1.291023506785735</v>
+        <v>1.317384516359875</v>
       </c>
       <c r="U58">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V58">
         <v>0.24</v>
       </c>
       <c r="W58">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>3.561981076249943</v>
+        <v>3.346626334551496</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.162754697212924</v>
+        <v>0.1624633032447694</v>
       </c>
       <c r="C59">
-        <v>240.469597514791</v>
+        <v>238.0287584350091</v>
       </c>
       <c r="D59">
-        <v>437.2605975147911</v>
+        <v>438.3527584350092</v>
       </c>
       <c r="E59">
-        <v>119.381</v>
+        <v>122.914</v>
       </c>
       <c r="F59">
-        <v>201.381</v>
+        <v>204.914</v>
       </c>
       <c r="G59">
         <v>4.59</v>
@@ -6125,28 +6125,28 @@
         <v>43.2</v>
       </c>
       <c r="M59">
-        <v>12.9085221</v>
+        <v>13.1349874</v>
       </c>
       <c r="N59">
-        <v>30.29147789999999</v>
+        <v>30.06501259999999</v>
       </c>
       <c r="O59">
-        <v>7.269954695999998</v>
+        <v>7.215603023999998</v>
       </c>
       <c r="P59">
-        <v>23.02152320399999</v>
+        <v>22.84940957599999</v>
       </c>
       <c r="Q59">
-        <v>31.821523204</v>
+        <v>31.649409576</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3139222725881954</v>
+        <v>0.3195429124875463</v>
       </c>
       <c r="T59">
-        <v>1.317384516359875</v>
+        <v>1.345000812104213</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.346626334551496</v>
+        <v>3.288925880507505</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1624633032447695</v>
+        <v>0.1621719092766149</v>
       </c>
       <c r="C60">
-        <v>238.028758435009</v>
+        <v>235.5933888728516</v>
       </c>
       <c r="D60">
-        <v>438.352758435009</v>
+        <v>439.4503888728516</v>
       </c>
       <c r="E60">
-        <v>122.914</v>
+        <v>126.447</v>
       </c>
       <c r="F60">
-        <v>204.914</v>
+        <v>208.447</v>
       </c>
       <c r="G60">
         <v>4.59</v>
@@ -6207,28 +6207,28 @@
         <v>43.2</v>
       </c>
       <c r="M60">
-        <v>13.1349874</v>
+        <v>13.3614527</v>
       </c>
       <c r="N60">
-        <v>30.0650126</v>
+        <v>29.83854729999999</v>
       </c>
       <c r="O60">
-        <v>7.215603023999999</v>
+        <v>7.161251351999998</v>
       </c>
       <c r="P60">
-        <v>22.849409576</v>
+        <v>22.677295948</v>
       </c>
       <c r="Q60">
-        <v>31.649409576</v>
+        <v>31.477295948</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3195429124875463</v>
+        <v>0.3254377299429631</v>
       </c>
       <c r="T60">
-        <v>1.345000812104213</v>
+        <v>1.373964244226322</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.288925880507506</v>
+        <v>3.233181374058226</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1621719092766149</v>
+        <v>0.1618805153084603</v>
       </c>
       <c r="C61">
-        <v>235.5933888728516</v>
+        <v>233.1635300182925</v>
       </c>
       <c r="D61">
-        <v>439.4503888728516</v>
+        <v>440.5535300182925</v>
       </c>
       <c r="E61">
-        <v>126.447</v>
+        <v>129.98</v>
       </c>
       <c r="F61">
-        <v>208.447</v>
+        <v>211.98</v>
       </c>
       <c r="G61">
         <v>4.59</v>
@@ -6289,28 +6289,28 @@
         <v>43.2</v>
       </c>
       <c r="M61">
-        <v>13.3614527</v>
+        <v>13.587918</v>
       </c>
       <c r="N61">
-        <v>29.83854729999999</v>
+        <v>29.61208199999999</v>
       </c>
       <c r="O61">
-        <v>7.161251351999998</v>
+        <v>7.106899679999998</v>
       </c>
       <c r="P61">
-        <v>22.677295948</v>
+        <v>22.50518232</v>
       </c>
       <c r="Q61">
-        <v>31.477295948</v>
+        <v>31.30518232</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3254377299429631</v>
+        <v>0.3316272882711507</v>
       </c>
       <c r="T61">
-        <v>1.373964244226322</v>
+        <v>1.404375847954538</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.233181374058226</v>
+        <v>3.179295017823922</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1618805153084603</v>
+        <v>0.1615891213403058</v>
       </c>
       <c r="C62">
-        <v>233.1635300182925</v>
+        <v>230.739223475938</v>
       </c>
       <c r="D62">
-        <v>440.5535300182925</v>
+        <v>441.662223475938</v>
       </c>
       <c r="E62">
-        <v>129.98</v>
+        <v>133.513</v>
       </c>
       <c r="F62">
-        <v>211.98</v>
+        <v>215.513</v>
       </c>
       <c r="G62">
         <v>4.59</v>
@@ -6371,28 +6371,28 @@
         <v>43.2</v>
       </c>
       <c r="M62">
-        <v>13.587918</v>
+        <v>13.8143833</v>
       </c>
       <c r="N62">
-        <v>29.61208199999999</v>
+        <v>29.38561669999999</v>
       </c>
       <c r="O62">
-        <v>7.106899679999998</v>
+        <v>7.052548007999998</v>
       </c>
       <c r="P62">
-        <v>22.50518232</v>
+        <v>22.33306869199999</v>
       </c>
       <c r="Q62">
-        <v>31.30518232</v>
+        <v>31.133068692</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3316272882711507</v>
+        <v>0.3381342598469378</v>
       </c>
       <c r="T62">
-        <v>1.404375847954538</v>
+        <v>1.436347021104713</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.179295017823922</v>
+        <v>3.127175427367792</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1615891213403058</v>
+        <v>0.1612977273721512</v>
       </c>
       <c r="C63">
-        <v>230.739223475938</v>
+        <v>228.3205112702592</v>
       </c>
       <c r="D63">
-        <v>441.662223475938</v>
+        <v>442.7765112702592</v>
       </c>
       <c r="E63">
-        <v>133.513</v>
+        <v>137.046</v>
       </c>
       <c r="F63">
-        <v>215.513</v>
+        <v>219.046</v>
       </c>
       <c r="G63">
         <v>4.59</v>
@@ -6453,28 +6453,28 @@
         <v>43.2</v>
       </c>
       <c r="M63">
-        <v>13.8143833</v>
+        <v>14.0408486</v>
       </c>
       <c r="N63">
-        <v>29.38561669999999</v>
+        <v>29.1591514</v>
       </c>
       <c r="O63">
-        <v>7.052548007999998</v>
+        <v>6.998196335999999</v>
       </c>
       <c r="P63">
-        <v>22.33306869199999</v>
+        <v>22.160955064</v>
       </c>
       <c r="Q63">
-        <v>31.133068692</v>
+        <v>30.960955064</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3381342598469378</v>
+        <v>0.3449837036109242</v>
       </c>
       <c r="T63">
-        <v>1.436347021104713</v>
+        <v>1.470000887578582</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.127175427367792</v>
+        <v>3.076737114023151</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1612977273721512</v>
+        <v>0.1610063334039966</v>
       </c>
       <c r="C64">
-        <v>228.3205112702592</v>
+        <v>225.9074358509004</v>
       </c>
       <c r="D64">
-        <v>442.7765112702592</v>
+        <v>443.8964358509004</v>
       </c>
       <c r="E64">
-        <v>137.046</v>
+        <v>140.579</v>
       </c>
       <c r="F64">
-        <v>219.046</v>
+        <v>222.579</v>
       </c>
       <c r="G64">
         <v>4.59</v>
@@ -6535,28 +6535,28 @@
         <v>43.2</v>
       </c>
       <c r="M64">
-        <v>14.0408486</v>
+        <v>14.2673139</v>
       </c>
       <c r="N64">
-        <v>29.1591514</v>
+        <v>28.93268609999999</v>
       </c>
       <c r="O64">
-        <v>6.998196335999999</v>
+        <v>6.943844663999998</v>
       </c>
       <c r="P64">
-        <v>22.160955064</v>
+        <v>21.98884143599999</v>
       </c>
       <c r="Q64">
-        <v>30.960955064</v>
+        <v>30.788841436</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3449837036109242</v>
+        <v>0.3522033875783692</v>
       </c>
       <c r="T64">
-        <v>1.470000887578582</v>
+        <v>1.505473881969956</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.076737114023151</v>
+        <v>3.027900016975164</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1610063334039966</v>
+        <v>0.1645088594358421</v>
       </c>
       <c r="C65">
-        <v>225.9074358509004</v>
+        <v>209.2771924825443</v>
       </c>
       <c r="D65">
-        <v>443.8964358509004</v>
+        <v>430.7991924825444</v>
       </c>
       <c r="E65">
-        <v>140.579</v>
+        <v>144.112</v>
       </c>
       <c r="F65">
-        <v>222.579</v>
+        <v>226.112</v>
       </c>
       <c r="G65">
         <v>4.59</v>
@@ -6617,45 +6617,45 @@
         <v>43.2</v>
       </c>
       <c r="M65">
-        <v>14.2673139</v>
+        <v>16.2574528</v>
       </c>
       <c r="N65">
-        <v>28.93268609999999</v>
+        <v>26.94254719999999</v>
       </c>
       <c r="O65">
-        <v>6.943844663999998</v>
+        <v>6.466211327999998</v>
       </c>
       <c r="P65">
-        <v>21.98884143599999</v>
+        <v>20.47633587199999</v>
       </c>
       <c r="Q65">
-        <v>30.788841436</v>
+        <v>29.276335872</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3522033875783692</v>
+        <v>0.3598241650995613</v>
       </c>
       <c r="T65">
-        <v>1.505473881969956</v>
+        <v>1.542917598271964</v>
       </c>
       <c r="U65">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V65">
         <v>0.24</v>
       </c>
       <c r="W65">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>3.027900016975164</v>
+        <v>2.657242836959059</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1645088594358421</v>
+        <v>0.1642767454676875</v>
       </c>
       <c r="C66">
-        <v>209.2771924825443</v>
+        <v>206.5881936377935</v>
       </c>
       <c r="D66">
-        <v>430.7991924825444</v>
+        <v>431.6431936377936</v>
       </c>
       <c r="E66">
-        <v>144.112</v>
+        <v>147.645</v>
       </c>
       <c r="F66">
-        <v>226.112</v>
+        <v>229.645</v>
       </c>
       <c r="G66">
         <v>4.59</v>
@@ -6699,28 +6699,28 @@
         <v>43.2</v>
       </c>
       <c r="M66">
-        <v>16.2574528</v>
+        <v>16.5114755</v>
       </c>
       <c r="N66">
-        <v>26.94254719999999</v>
+        <v>26.68852449999999</v>
       </c>
       <c r="O66">
-        <v>6.466211327999998</v>
+        <v>6.405245879999998</v>
       </c>
       <c r="P66">
-        <v>20.47633587199999</v>
+        <v>20.28327861999999</v>
       </c>
       <c r="Q66">
-        <v>29.276335872</v>
+        <v>29.08327862</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3598241650995613</v>
+        <v>0.3678804156219644</v>
       </c>
       <c r="T66">
-        <v>1.542917598271964</v>
+        <v>1.582500955505514</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.657242836959059</v>
+        <v>2.616362177928919</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1642767454676875</v>
+        <v>0.164044631499533</v>
       </c>
       <c r="C67">
-        <v>206.5881936377935</v>
+        <v>203.9025083381025</v>
       </c>
       <c r="D67">
-        <v>431.6431936377936</v>
+        <v>432.4905083381025</v>
       </c>
       <c r="E67">
-        <v>147.645</v>
+        <v>151.178</v>
       </c>
       <c r="F67">
-        <v>229.645</v>
+        <v>233.178</v>
       </c>
       <c r="G67">
         <v>4.59</v>
@@ -6781,28 +6781,28 @@
         <v>43.2</v>
       </c>
       <c r="M67">
-        <v>16.5114755</v>
+        <v>16.7654982</v>
       </c>
       <c r="N67">
-        <v>26.68852449999999</v>
+        <v>26.43450179999999</v>
       </c>
       <c r="O67">
-        <v>6.405245879999998</v>
+        <v>6.344280431999998</v>
       </c>
       <c r="P67">
-        <v>20.28327861999999</v>
+        <v>20.09022136799999</v>
       </c>
       <c r="Q67">
-        <v>29.08327862</v>
+        <v>28.890221368</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3678804156219644</v>
+        <v>0.3764105632339205</v>
       </c>
       <c r="T67">
-        <v>1.582500955505514</v>
+        <v>1.624412745517509</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.616362177928919</v>
+        <v>2.576720326748178</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.164044631499533</v>
+        <v>0.1638125175313784</v>
       </c>
       <c r="C68">
-        <v>203.9025083381025</v>
+        <v>201.2201561352979</v>
       </c>
       <c r="D68">
-        <v>432.4905083381025</v>
+        <v>433.341156135298</v>
       </c>
       <c r="E68">
-        <v>151.178</v>
+        <v>154.711</v>
       </c>
       <c r="F68">
-        <v>233.178</v>
+        <v>236.711</v>
       </c>
       <c r="G68">
         <v>4.59</v>
@@ -6863,28 +6863,28 @@
         <v>43.2</v>
       </c>
       <c r="M68">
-        <v>16.7654982</v>
+        <v>17.0195209</v>
       </c>
       <c r="N68">
-        <v>26.43450179999999</v>
+        <v>26.18047909999999</v>
       </c>
       <c r="O68">
-        <v>6.344280431999998</v>
+        <v>6.283314983999998</v>
       </c>
       <c r="P68">
-        <v>20.09022136799999</v>
+        <v>19.897164116</v>
       </c>
       <c r="Q68">
-        <v>28.890221368</v>
+        <v>28.697164116</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3764105632339205</v>
+        <v>0.3854576894890254</v>
       </c>
       <c r="T68">
-        <v>1.624412745517509</v>
+        <v>1.668864644015078</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.576720326748178</v>
+        <v>2.538261814408653</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1638125175313784</v>
+        <v>0.1635804035632238</v>
       </c>
       <c r="C69">
-        <v>201.2201561352979</v>
+        <v>198.541156735332</v>
       </c>
       <c r="D69">
-        <v>433.341156135298</v>
+        <v>434.195156735332</v>
       </c>
       <c r="E69">
-        <v>154.711</v>
+        <v>158.244</v>
       </c>
       <c r="F69">
-        <v>236.711</v>
+        <v>240.244</v>
       </c>
       <c r="G69">
         <v>4.59</v>
@@ -6945,28 +6945,28 @@
         <v>43.2</v>
       </c>
       <c r="M69">
-        <v>17.0195209</v>
+        <v>17.2735436</v>
       </c>
       <c r="N69">
-        <v>26.18047909999999</v>
+        <v>25.92645639999999</v>
       </c>
       <c r="O69">
-        <v>6.283314983999998</v>
+        <v>6.222349535999998</v>
       </c>
       <c r="P69">
-        <v>19.897164116</v>
+        <v>19.704106864</v>
       </c>
       <c r="Q69">
-        <v>28.697164116</v>
+        <v>28.504106864</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3854576894890254</v>
+        <v>0.3950702611350745</v>
       </c>
       <c r="T69">
-        <v>1.668864644015078</v>
+        <v>1.716094786168746</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.538261814408653</v>
+        <v>2.500934434784996</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1635804035632238</v>
+        <v>0.1653934495950693</v>
       </c>
       <c r="C70">
-        <v>198.541156735332</v>
+        <v>188.4257242640642</v>
       </c>
       <c r="D70">
-        <v>434.195156735332</v>
+        <v>427.6127242640642</v>
       </c>
       <c r="E70">
-        <v>158.244</v>
+        <v>161.777</v>
       </c>
       <c r="F70">
-        <v>240.244</v>
+        <v>243.777</v>
       </c>
       <c r="G70">
         <v>4.59</v>
@@ -7027,45 +7027,45 @@
         <v>43.2</v>
       </c>
       <c r="M70">
-        <v>17.2735436</v>
+        <v>18.4782966</v>
       </c>
       <c r="N70">
-        <v>25.92645639999999</v>
+        <v>24.72170339999999</v>
       </c>
       <c r="O70">
-        <v>6.222349535999998</v>
+        <v>5.933208815999998</v>
       </c>
       <c r="P70">
-        <v>19.704106864</v>
+        <v>18.788494584</v>
       </c>
       <c r="Q70">
-        <v>28.504106864</v>
+        <v>27.588494584</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3950702611350745</v>
+        <v>0.4053029986937719</v>
       </c>
       <c r="T70">
-        <v>1.716094786168746</v>
+        <v>1.766372034267812</v>
       </c>
       <c r="U70">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V70">
         <v>0.24</v>
       </c>
       <c r="W70">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y70">
-        <v>2.500934434784996</v>
+        <v>2.337877832310581</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1653934495950693</v>
+        <v>0.1651909756269147</v>
       </c>
       <c r="C71">
-        <v>188.4257242640642</v>
+        <v>185.617908430292</v>
       </c>
       <c r="D71">
-        <v>427.6127242640642</v>
+        <v>428.3379084302921</v>
       </c>
       <c r="E71">
-        <v>161.777</v>
+        <v>165.31</v>
       </c>
       <c r="F71">
-        <v>243.777</v>
+        <v>247.31</v>
       </c>
       <c r="G71">
         <v>4.59</v>
@@ -7109,28 +7109,28 @@
         <v>43.2</v>
       </c>
       <c r="M71">
-        <v>18.4782966</v>
+        <v>18.746098</v>
       </c>
       <c r="N71">
-        <v>24.72170339999999</v>
+        <v>24.45390199999999</v>
       </c>
       <c r="O71">
-        <v>5.933208815999998</v>
+        <v>5.868936479999998</v>
       </c>
       <c r="P71">
-        <v>18.788494584</v>
+        <v>18.58496551999999</v>
       </c>
       <c r="Q71">
-        <v>27.588494584</v>
+        <v>27.38496552</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4053029986937719</v>
+        <v>0.4162179187563824</v>
       </c>
       <c r="T71">
-        <v>1.766372034267812</v>
+        <v>1.820001098906816</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.337877832310581</v>
+        <v>2.304479577563288</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1651909756269147</v>
+        <v>0.1649885016587602</v>
       </c>
       <c r="C72">
-        <v>185.617908430292</v>
+        <v>182.8125564401579</v>
       </c>
       <c r="D72">
-        <v>428.3379084302921</v>
+        <v>429.065556440158</v>
       </c>
       <c r="E72">
-        <v>165.31</v>
+        <v>168.843</v>
       </c>
       <c r="F72">
-        <v>247.31</v>
+        <v>250.843</v>
       </c>
       <c r="G72">
         <v>4.59</v>
@@ -7191,28 +7191,28 @@
         <v>43.2</v>
       </c>
       <c r="M72">
-        <v>18.746098</v>
+        <v>19.01389940000001</v>
       </c>
       <c r="N72">
-        <v>24.45390199999999</v>
+        <v>24.18610059999999</v>
       </c>
       <c r="O72">
-        <v>5.868936479999998</v>
+        <v>5.804664143999998</v>
       </c>
       <c r="P72">
-        <v>18.58496551999999</v>
+        <v>18.38143645599999</v>
       </c>
       <c r="Q72">
-        <v>27.38496552</v>
+        <v>27.181436456</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4162179187563824</v>
+        <v>0.4278855919267592</v>
       </c>
       <c r="T72">
-        <v>1.820001098906816</v>
+        <v>1.87732871972782</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.304479577563288</v>
+        <v>2.272022118724367</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1649885016587602</v>
+        <v>0.1647860276906056</v>
       </c>
       <c r="C73">
-        <v>182.812556440158</v>
+        <v>180.0096808715474</v>
       </c>
       <c r="D73">
-        <v>429.065556440158</v>
+        <v>429.7956808715475</v>
       </c>
       <c r="E73">
-        <v>168.843</v>
+        <v>172.376</v>
       </c>
       <c r="F73">
-        <v>250.843</v>
+        <v>254.376</v>
       </c>
       <c r="G73">
         <v>4.59</v>
@@ -7273,28 +7273,28 @@
         <v>43.2</v>
       </c>
       <c r="M73">
-        <v>19.0138994</v>
+        <v>19.2817008</v>
       </c>
       <c r="N73">
-        <v>24.1861006</v>
+        <v>23.91829919999999</v>
       </c>
       <c r="O73">
-        <v>5.804664143999998</v>
+        <v>5.740391807999998</v>
       </c>
       <c r="P73">
-        <v>18.381436456</v>
+        <v>18.17790739199999</v>
       </c>
       <c r="Q73">
-        <v>27.181436456</v>
+        <v>26.977907392</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4278855919267591</v>
+        <v>0.4403866703235913</v>
       </c>
       <c r="T73">
-        <v>1.877328719727819</v>
+        <v>1.938751170607466</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.272022118724368</v>
+        <v>2.240466255964307</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1647860276906056</v>
+        <v>0.164583553722451</v>
       </c>
       <c r="C74">
-        <v>180.0096808715474</v>
+        <v>177.2092943881046</v>
       </c>
       <c r="D74">
-        <v>429.7956808715475</v>
+        <v>430.5282943881046</v>
       </c>
       <c r="E74">
-        <v>172.376</v>
+        <v>175.909</v>
       </c>
       <c r="F74">
-        <v>254.376</v>
+        <v>257.909</v>
       </c>
       <c r="G74">
         <v>4.59</v>
@@ -7355,28 +7355,28 @@
         <v>43.2</v>
       </c>
       <c r="M74">
-        <v>19.2817008</v>
+        <v>19.5495022</v>
       </c>
       <c r="N74">
-        <v>23.91829919999999</v>
+        <v>23.65049779999999</v>
       </c>
       <c r="O74">
-        <v>5.740391807999998</v>
+        <v>5.676119471999998</v>
       </c>
       <c r="P74">
-        <v>18.17790739199999</v>
+        <v>17.97437832799999</v>
       </c>
       <c r="Q74">
-        <v>26.977907392</v>
+        <v>26.774378328</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4403866703235913</v>
+        <v>0.4538137545275963</v>
       </c>
       <c r="T74">
-        <v>1.938751170607466</v>
+        <v>2.004723432663383</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.240466255964307</v>
+        <v>2.209774937389454</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.164583553722451</v>
+        <v>0.1643810797542964</v>
       </c>
       <c r="C75">
-        <v>177.2092943881046</v>
+        <v>174.411409739965</v>
       </c>
       <c r="D75">
-        <v>430.5282943881046</v>
+        <v>431.263409739965</v>
       </c>
       <c r="E75">
-        <v>175.909</v>
+        <v>179.442</v>
       </c>
       <c r="F75">
-        <v>257.909</v>
+        <v>261.442</v>
       </c>
       <c r="G75">
         <v>4.59</v>
@@ -7437,28 +7437,28 @@
         <v>43.2</v>
       </c>
       <c r="M75">
-        <v>19.5495022</v>
+        <v>19.8173036</v>
       </c>
       <c r="N75">
-        <v>23.65049779999999</v>
+        <v>23.38269639999999</v>
       </c>
       <c r="O75">
-        <v>5.676119471999998</v>
+        <v>5.611847135999998</v>
       </c>
       <c r="P75">
-        <v>17.97437832799999</v>
+        <v>17.770849264</v>
       </c>
       <c r="Q75">
-        <v>26.774378328</v>
+        <v>26.570849264</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4538137545275963</v>
+        <v>0.4682736913626785</v>
       </c>
       <c r="T75">
-        <v>2.004723432663383</v>
+        <v>2.075770484108217</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.209774937389454</v>
+        <v>2.179913113911218</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1643810797542964</v>
+        <v>0.1641786057861419</v>
       </c>
       <c r="C76">
-        <v>174.411409739965</v>
+        <v>171.6160397644954</v>
       </c>
       <c r="D76">
-        <v>431.263409739965</v>
+        <v>432.0010397644955</v>
       </c>
       <c r="E76">
-        <v>179.442</v>
+        <v>182.975</v>
       </c>
       <c r="F76">
-        <v>261.442</v>
+        <v>264.975</v>
       </c>
       <c r="G76">
         <v>4.59</v>
@@ -7519,28 +7519,28 @@
         <v>43.2</v>
       </c>
       <c r="M76">
-        <v>19.8173036</v>
+        <v>20.085105</v>
       </c>
       <c r="N76">
-        <v>23.38269639999999</v>
+        <v>23.11489499999999</v>
       </c>
       <c r="O76">
-        <v>5.611847135999998</v>
+        <v>5.547574799999998</v>
       </c>
       <c r="P76">
-        <v>17.770849264</v>
+        <v>17.5673202</v>
       </c>
       <c r="Q76">
-        <v>26.570849264</v>
+        <v>26.3673202</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4682736913626785</v>
+        <v>0.4838904231445675</v>
       </c>
       <c r="T76">
-        <v>2.075770484108217</v>
+        <v>2.152501299668637</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.179913113911218</v>
+        <v>2.150847605725735</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1641786057861419</v>
+        <v>0.1639761318179873</v>
       </c>
       <c r="C77">
-        <v>171.6160397644954</v>
+        <v>168.8231973870409</v>
       </c>
       <c r="D77">
-        <v>432.0010397644955</v>
+        <v>432.7411973870409</v>
       </c>
       <c r="E77">
-        <v>182.975</v>
+        <v>186.508</v>
       </c>
       <c r="F77">
-        <v>264.975</v>
+        <v>268.508</v>
       </c>
       <c r="G77">
         <v>4.59</v>
@@ -7601,28 +7601,28 @@
         <v>43.2</v>
       </c>
       <c r="M77">
-        <v>20.085105</v>
+        <v>20.35290640000001</v>
       </c>
       <c r="N77">
-        <v>23.11489499999999</v>
+        <v>22.84709359999999</v>
       </c>
       <c r="O77">
-        <v>5.547574799999998</v>
+        <v>5.483302463999998</v>
       </c>
       <c r="P77">
-        <v>17.5673202</v>
+        <v>17.36379113599999</v>
       </c>
       <c r="Q77">
-        <v>26.3673202</v>
+        <v>26.163791136</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4838904231445675</v>
+        <v>0.5008085492416139</v>
       </c>
       <c r="T77">
-        <v>2.152501299668637</v>
+        <v>2.235626349859093</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.150847605725735</v>
+        <v>2.122546979334607</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1639761318179873</v>
+        <v>0.1637736578498328</v>
       </c>
       <c r="C78">
-        <v>168.8231973870409</v>
+        <v>166.0328956216794</v>
       </c>
       <c r="D78">
-        <v>432.7411973870409</v>
+        <v>433.4838956216794</v>
       </c>
       <c r="E78">
-        <v>186.508</v>
+        <v>190.041</v>
       </c>
       <c r="F78">
-        <v>268.508</v>
+        <v>272.041</v>
       </c>
       <c r="G78">
         <v>4.59</v>
@@ -7683,28 +7683,28 @@
         <v>43.2</v>
       </c>
       <c r="M78">
-        <v>20.35290640000001</v>
+        <v>20.6207078</v>
       </c>
       <c r="N78">
-        <v>22.84709359999999</v>
+        <v>22.57929219999999</v>
       </c>
       <c r="O78">
-        <v>5.483302463999998</v>
+        <v>5.419030127999998</v>
       </c>
       <c r="P78">
-        <v>17.36379113599999</v>
+        <v>17.16026207199999</v>
       </c>
       <c r="Q78">
-        <v>26.163791136</v>
+        <v>25.960262072</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5008085492416139</v>
+        <v>0.5191978167384034</v>
       </c>
       <c r="T78">
-        <v>2.235626349859093</v>
+        <v>2.325979665283501</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.122546979334607</v>
+        <v>2.094981434148443</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1637736578498328</v>
+        <v>0.1635711838816782</v>
       </c>
       <c r="C79">
-        <v>166.0328956216794</v>
+        <v>163.2451475719849</v>
       </c>
       <c r="D79">
-        <v>433.4838956216794</v>
+        <v>434.2291475719849</v>
       </c>
       <c r="E79">
-        <v>190.041</v>
+        <v>193.574</v>
       </c>
       <c r="F79">
-        <v>272.041</v>
+        <v>275.574</v>
       </c>
       <c r="G79">
         <v>4.59</v>
@@ -7765,28 +7765,28 @@
         <v>43.2</v>
       </c>
       <c r="M79">
-        <v>20.6207078</v>
+        <v>20.8885092</v>
       </c>
       <c r="N79">
-        <v>22.57929219999999</v>
+        <v>22.31149079999999</v>
       </c>
       <c r="O79">
-        <v>5.419030127999998</v>
+        <v>5.354757791999998</v>
       </c>
       <c r="P79">
-        <v>17.16026207199999</v>
+        <v>16.956733008</v>
       </c>
       <c r="Q79">
-        <v>25.960262072</v>
+        <v>25.756733008</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5191978167384034</v>
+        <v>0.53925883582581</v>
       </c>
       <c r="T79">
-        <v>2.325979665283501</v>
+        <v>2.424546918473765</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.094981434148443</v>
+        <v>2.068122697813207</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1635711838816782</v>
+        <v>0.1633687099135236</v>
       </c>
       <c r="C80">
-        <v>163.2451475719849</v>
+        <v>160.4599664317984</v>
       </c>
       <c r="D80">
-        <v>434.2291475719849</v>
+        <v>434.9769664317984</v>
       </c>
       <c r="E80">
-        <v>193.574</v>
+        <v>197.107</v>
       </c>
       <c r="F80">
-        <v>275.574</v>
+        <v>279.107</v>
       </c>
       <c r="G80">
         <v>4.59</v>
@@ -7847,28 +7847,28 @@
         <v>43.2</v>
       </c>
       <c r="M80">
-        <v>20.8885092</v>
+        <v>21.1563106</v>
       </c>
       <c r="N80">
-        <v>22.31149079999999</v>
+        <v>22.04368939999999</v>
       </c>
       <c r="O80">
-        <v>5.354757791999998</v>
+        <v>5.290485455999997</v>
       </c>
       <c r="P80">
-        <v>16.956733008</v>
+        <v>16.75320394399999</v>
       </c>
       <c r="Q80">
-        <v>25.756733008</v>
+        <v>25.553203944</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.53925883582581</v>
+        <v>0.5612304281596364</v>
       </c>
       <c r="T80">
-        <v>2.424546918473765</v>
+        <v>2.53250152911072</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.068122697813207</v>
+        <v>2.041943929486457</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1633687099135236</v>
+        <v>0.1631662359453691</v>
       </c>
       <c r="C81">
-        <v>160.4599664317984</v>
+        <v>157.6773654860057</v>
       </c>
       <c r="D81">
-        <v>434.9769664317984</v>
+        <v>435.7273654860058</v>
       </c>
       <c r="E81">
-        <v>197.107</v>
+        <v>200.64</v>
       </c>
       <c r="F81">
-        <v>279.107</v>
+        <v>282.64</v>
       </c>
       <c r="G81">
         <v>4.59</v>
@@ -7929,28 +7929,28 @@
         <v>43.2</v>
       </c>
       <c r="M81">
-        <v>21.1563106</v>
+        <v>21.424112</v>
       </c>
       <c r="N81">
-        <v>22.04368939999999</v>
+        <v>21.77588799999999</v>
       </c>
       <c r="O81">
-        <v>5.290485455999997</v>
+        <v>5.226213119999998</v>
       </c>
       <c r="P81">
-        <v>16.75320394399999</v>
+        <v>16.54967487999999</v>
       </c>
       <c r="Q81">
-        <v>25.553203944</v>
+        <v>25.34967488</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5612304281596364</v>
+        <v>0.5853991797268455</v>
       </c>
       <c r="T81">
-        <v>2.53250152911072</v>
+        <v>2.651251600811371</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.041943929486457</v>
+        <v>2.016419630367877</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1631662359453691</v>
+        <v>0.1717052819772145</v>
       </c>
       <c r="C82">
-        <v>157.6773654860057</v>
+        <v>124.5928171094008</v>
       </c>
       <c r="D82">
-        <v>435.7273654860058</v>
+        <v>406.1758171094008</v>
       </c>
       <c r="E82">
-        <v>200.64</v>
+        <v>204.173</v>
       </c>
       <c r="F82">
-        <v>282.64</v>
+        <v>286.173</v>
       </c>
       <c r="G82">
         <v>4.59</v>
@@ -8011,45 +8011,45 @@
         <v>43.2</v>
       </c>
       <c r="M82">
-        <v>21.424112</v>
+        <v>25.75557</v>
       </c>
       <c r="N82">
-        <v>21.77588799999999</v>
+        <v>17.44443</v>
       </c>
       <c r="O82">
-        <v>5.226213119999998</v>
+        <v>4.186663199999999</v>
       </c>
       <c r="P82">
-        <v>16.54967487999999</v>
+        <v>13.2577668</v>
       </c>
       <c r="Q82">
-        <v>25.34967488</v>
+        <v>22.0577668</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5853991797268455</v>
+        <v>0.6121120104063923</v>
       </c>
       <c r="T82">
-        <v>2.651251600811371</v>
+        <v>2.782501680059459</v>
       </c>
       <c r="U82">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V82">
         <v>0.24</v>
       </c>
       <c r="W82">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.016419630367877</v>
+        <v>1.677307083477477</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1717052819772145</v>
+        <v>0.17161072800906</v>
       </c>
       <c r="C83">
-        <v>124.5928171094008</v>
+        <v>121.3650815004736</v>
       </c>
       <c r="D83">
-        <v>406.1758171094008</v>
+        <v>406.4810815004736</v>
       </c>
       <c r="E83">
-        <v>204.173</v>
+        <v>207.706</v>
       </c>
       <c r="F83">
-        <v>286.173</v>
+        <v>289.706</v>
       </c>
       <c r="G83">
         <v>4.59</v>
@@ -8093,28 +8093,28 @@
         <v>43.2</v>
       </c>
       <c r="M83">
-        <v>25.75557</v>
+        <v>26.07354</v>
       </c>
       <c r="N83">
-        <v>17.44443</v>
+        <v>17.12645999999999</v>
       </c>
       <c r="O83">
-        <v>4.186663199999999</v>
+        <v>4.110350399999999</v>
       </c>
       <c r="P83">
-        <v>13.2577668</v>
+        <v>13.0161096</v>
       </c>
       <c r="Q83">
-        <v>22.0577668</v>
+        <v>21.8161096</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6121120104063923</v>
+        <v>0.6417929333836666</v>
       </c>
       <c r="T83">
-        <v>2.782501680059459</v>
+        <v>2.928335101446223</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.677307083477477</v>
+        <v>1.656852119044824</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.17161072800906</v>
+        <v>0.1715161740409054</v>
       </c>
       <c r="C84">
-        <v>121.3650815004736</v>
+        <v>118.1378050840049</v>
       </c>
       <c r="D84">
-        <v>406.4810815004736</v>
+        <v>406.786805084005</v>
       </c>
       <c r="E84">
-        <v>207.706</v>
+        <v>211.239</v>
       </c>
       <c r="F84">
-        <v>289.706</v>
+        <v>293.239</v>
       </c>
       <c r="G84">
         <v>4.59</v>
@@ -8175,28 +8175,28 @@
         <v>43.2</v>
       </c>
       <c r="M84">
-        <v>26.07354</v>
+        <v>26.39151</v>
       </c>
       <c r="N84">
-        <v>17.12645999999999</v>
+        <v>16.80849</v>
       </c>
       <c r="O84">
-        <v>4.110350399999999</v>
+        <v>4.034037599999999</v>
       </c>
       <c r="P84">
-        <v>13.0161096</v>
+        <v>12.7744524</v>
       </c>
       <c r="Q84">
-        <v>21.8161096</v>
+        <v>21.5744524</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6417929333836666</v>
+        <v>0.6749657296523849</v>
       </c>
       <c r="T84">
-        <v>2.928335101446223</v>
+        <v>3.091325395937313</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.656852119044824</v>
+        <v>1.636890045321393</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1715161740409054</v>
+        <v>0.1714216200727508</v>
       </c>
       <c r="C85">
-        <v>118.1378050840049</v>
+        <v>114.9109888968815</v>
       </c>
       <c r="D85">
-        <v>406.786805084005</v>
+        <v>407.0929888968815</v>
       </c>
       <c r="E85">
-        <v>211.239</v>
+        <v>214.772</v>
       </c>
       <c r="F85">
-        <v>293.239</v>
+        <v>296.772</v>
       </c>
       <c r="G85">
         <v>4.59</v>
@@ -8257,28 +8257,28 @@
         <v>43.2</v>
       </c>
       <c r="M85">
-        <v>26.39151</v>
+        <v>26.70948</v>
       </c>
       <c r="N85">
-        <v>16.80849</v>
+        <v>16.49051999999999</v>
       </c>
       <c r="O85">
-        <v>4.034037599999999</v>
+        <v>3.957724799999998</v>
       </c>
       <c r="P85">
-        <v>12.7744524</v>
+        <v>12.5327952</v>
       </c>
       <c r="Q85">
-        <v>21.5744524</v>
+        <v>21.3327952</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6749657296523849</v>
+        <v>0.712285125454693</v>
       </c>
       <c r="T85">
-        <v>3.091325395937313</v>
+        <v>3.274689477239789</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.636890045321393</v>
+        <v>1.617403259067567</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1714216200727508</v>
+        <v>0.1713270661045963</v>
       </c>
       <c r="C86">
-        <v>114.9109888968815</v>
+        <v>111.6846339791144</v>
       </c>
       <c r="D86">
-        <v>407.0929888968815</v>
+        <v>407.3996339791144</v>
       </c>
       <c r="E86">
-        <v>214.772</v>
+        <v>218.305</v>
       </c>
       <c r="F86">
-        <v>296.772</v>
+        <v>300.305</v>
       </c>
       <c r="G86">
         <v>4.59</v>
@@ -8339,28 +8339,28 @@
         <v>43.2</v>
       </c>
       <c r="M86">
-        <v>26.70948</v>
+        <v>27.02745</v>
       </c>
       <c r="N86">
-        <v>16.49052</v>
+        <v>16.17255</v>
       </c>
       <c r="O86">
-        <v>3.957724799999999</v>
+        <v>3.881411999999999</v>
       </c>
       <c r="P86">
-        <v>12.5327952</v>
+        <v>12.291138</v>
       </c>
       <c r="Q86">
-        <v>21.3327952</v>
+        <v>21.091138</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.7122851254546926</v>
+        <v>0.7545804406973085</v>
       </c>
       <c r="T86">
-        <v>3.274689477239786</v>
+        <v>3.482502102715926</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.617403259067567</v>
+        <v>1.598374985431478</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1713270661045963</v>
+        <v>0.1712325121364417</v>
       </c>
       <c r="C87">
-        <v>111.6846339791144</v>
+        <v>108.4587413738506</v>
       </c>
       <c r="D87">
-        <v>407.3996339791144</v>
+        <v>407.7067413738507</v>
       </c>
       <c r="E87">
-        <v>218.305</v>
+        <v>221.838</v>
       </c>
       <c r="F87">
-        <v>300.305</v>
+        <v>303.838</v>
       </c>
       <c r="G87">
         <v>4.59</v>
@@ -8421,28 +8421,28 @@
         <v>43.2</v>
       </c>
       <c r="M87">
-        <v>27.02745</v>
+        <v>27.34542</v>
       </c>
       <c r="N87">
-        <v>16.17255</v>
+        <v>15.85458</v>
       </c>
       <c r="O87">
-        <v>3.881411999999999</v>
+        <v>3.805099199999999</v>
       </c>
       <c r="P87">
-        <v>12.291138</v>
+        <v>12.0494808</v>
       </c>
       <c r="Q87">
-        <v>21.091138</v>
+        <v>20.8494808</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7545804406973085</v>
+        <v>0.8029179438317263</v>
       </c>
       <c r="T87">
-        <v>3.482502102715926</v>
+        <v>3.720002246117227</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.598374985431478</v>
+        <v>1.579789229786926</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1712325121364417</v>
+        <v>0.1711379581682871</v>
       </c>
       <c r="C88">
-        <v>108.4587413738506</v>
+        <v>105.2333121273849</v>
       </c>
       <c r="D88">
-        <v>407.7067413738507</v>
+        <v>408.0143121273849</v>
       </c>
       <c r="E88">
-        <v>221.838</v>
+        <v>225.371</v>
       </c>
       <c r="F88">
-        <v>303.838</v>
+        <v>307.371</v>
       </c>
       <c r="G88">
         <v>4.59</v>
@@ -8503,28 +8503,28 @@
         <v>43.2</v>
       </c>
       <c r="M88">
-        <v>27.34542</v>
+        <v>27.66339</v>
       </c>
       <c r="N88">
-        <v>15.85458</v>
+        <v>15.53661</v>
       </c>
       <c r="O88">
-        <v>3.805099199999999</v>
+        <v>3.7287864</v>
       </c>
       <c r="P88">
-        <v>12.0494808</v>
+        <v>11.8078236</v>
       </c>
       <c r="Q88">
-        <v>20.8494808</v>
+        <v>20.6078236</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.8029179438317263</v>
+        <v>0.858691985909901</v>
       </c>
       <c r="T88">
-        <v>3.720002246117227</v>
+        <v>3.994040873118728</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.579789229786926</v>
+        <v>1.561630732892823</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1711379581682871</v>
+        <v>0.1710434042001326</v>
       </c>
       <c r="C89">
-        <v>105.2333121273849</v>
+        <v>102.0083472891716</v>
       </c>
       <c r="D89">
-        <v>408.0143121273849</v>
+        <v>408.3223472891716</v>
       </c>
       <c r="E89">
-        <v>225.371</v>
+        <v>228.904</v>
       </c>
       <c r="F89">
-        <v>307.371</v>
+        <v>310.904</v>
       </c>
       <c r="G89">
         <v>4.59</v>
@@ -8585,28 +8585,28 @@
         <v>43.2</v>
       </c>
       <c r="M89">
-        <v>27.66339</v>
+        <v>27.98136</v>
       </c>
       <c r="N89">
-        <v>15.53661</v>
+        <v>15.21864</v>
       </c>
       <c r="O89">
-        <v>3.7287864</v>
+        <v>3.652473599999999</v>
       </c>
       <c r="P89">
-        <v>11.8078236</v>
+        <v>11.5661664</v>
       </c>
       <c r="Q89">
-        <v>20.6078236</v>
+        <v>20.3661664</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.858691985909901</v>
+        <v>0.9237617016677715</v>
       </c>
       <c r="T89">
-        <v>3.994040873118728</v>
+        <v>4.313752604620481</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.561630732892823</v>
+        <v>1.54388492910995</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1710434042001326</v>
+        <v>0.170948850231978</v>
       </c>
       <c r="C90">
-        <v>102.0083472891716</v>
+        <v>98.78384791183652</v>
       </c>
       <c r="D90">
-        <v>408.3223472891716</v>
+        <v>408.6308479118366</v>
       </c>
       <c r="E90">
-        <v>228.904</v>
+        <v>232.437</v>
       </c>
       <c r="F90">
-        <v>310.904</v>
+        <v>314.437</v>
       </c>
       <c r="G90">
         <v>4.59</v>
@@ -8667,28 +8667,28 @@
         <v>43.2</v>
       </c>
       <c r="M90">
-        <v>27.98136</v>
+        <v>28.29933</v>
       </c>
       <c r="N90">
-        <v>15.21864</v>
+        <v>14.90066999999999</v>
       </c>
       <c r="O90">
-        <v>3.652473599999999</v>
+        <v>3.576160799999998</v>
       </c>
       <c r="P90">
-        <v>11.5661664</v>
+        <v>11.3245092</v>
       </c>
       <c r="Q90">
-        <v>20.3661664</v>
+        <v>20.1245092</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.9237617016677715</v>
+        <v>1.000662274836164</v>
       </c>
       <c r="T90">
-        <v>4.313752604620481</v>
+        <v>4.691593741849824</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.54388492910995</v>
+        <v>1.526537907434558</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.170948850231978</v>
+        <v>0.1708542962638235</v>
       </c>
       <c r="C91">
-        <v>98.78384791183652</v>
+        <v>95.55981505118939</v>
       </c>
       <c r="D91">
-        <v>408.6308479118366</v>
+        <v>408.9398150511894</v>
       </c>
       <c r="E91">
-        <v>232.437</v>
+        <v>235.97</v>
       </c>
       <c r="F91">
-        <v>314.437</v>
+        <v>317.97</v>
       </c>
       <c r="G91">
         <v>4.59</v>
@@ -8749,28 +8749,28 @@
         <v>43.2</v>
       </c>
       <c r="M91">
-        <v>28.29933</v>
+        <v>28.6173</v>
       </c>
       <c r="N91">
-        <v>14.90066999999999</v>
+        <v>14.5827</v>
       </c>
       <c r="O91">
-        <v>3.576160799999998</v>
+        <v>3.499847999999999</v>
       </c>
       <c r="P91">
-        <v>11.3245092</v>
+        <v>11.082852</v>
       </c>
       <c r="Q91">
-        <v>20.1245092</v>
+        <v>19.882852</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.000662274836164</v>
+        <v>1.092942962638235</v>
       </c>
       <c r="T91">
-        <v>4.691593741849824</v>
+        <v>5.145003106525037</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.526537907434558</v>
+        <v>1.509576375129729</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1708542962638235</v>
+        <v>0.2152277458316308</v>
       </c>
       <c r="C92">
-        <v>95.55981505118939</v>
+        <v>-15.07530196260313</v>
       </c>
       <c r="D92">
-        <v>408.9398150511894</v>
+        <v>301.8376980373969</v>
       </c>
       <c r="E92">
-        <v>235.97</v>
+        <v>239.503</v>
       </c>
       <c r="F92">
-        <v>317.97</v>
+        <v>321.503</v>
       </c>
       <c r="G92">
         <v>4.59</v>
@@ -8831,45 +8831,45 @@
         <v>43.2</v>
       </c>
       <c r="M92">
-        <v>28.6173</v>
+        <v>47.19664040000001</v>
       </c>
       <c r="N92">
-        <v>14.5827</v>
+        <v>-3.996640400000018</v>
       </c>
       <c r="O92">
-        <v>3.499847999999999</v>
+        <v>-0.9591936960000044</v>
       </c>
       <c r="P92">
-        <v>11.082852</v>
+        <v>-3.037446704000014</v>
       </c>
       <c r="Q92">
-        <v>19.882852</v>
+        <v>5.76255329599999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.092942962638235</v>
+        <v>1.233176784046142</v>
       </c>
       <c r="T92">
-        <v>5.145003106525037</v>
+        <v>5.83402406405099</v>
       </c>
       <c r="U92">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.24</v>
+        <v>0.2196766530865192</v>
       </c>
       <c r="W92">
-        <v>0.0684</v>
+        <v>0.114551467326899</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y92">
-        <v>1.509576375129729</v>
+        <v>0.9153193878604966</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2152277458316308</v>
+        <v>0.2162377458316308</v>
       </c>
       <c r="C93">
-        <v>-15.07530196260313</v>
+        <v>-20.39696722293172</v>
       </c>
       <c r="D93">
-        <v>301.8376980373969</v>
+        <v>300.0490327770683</v>
       </c>
       <c r="E93">
-        <v>239.503</v>
+        <v>243.036</v>
       </c>
       <c r="F93">
-        <v>321.503</v>
+        <v>325.036</v>
       </c>
       <c r="G93">
         <v>4.59</v>
@@ -8913,37 +8913,37 @@
         <v>43.2</v>
       </c>
       <c r="M93">
-        <v>47.19664040000001</v>
+        <v>47.71528480000001</v>
       </c>
       <c r="N93">
-        <v>-3.996640400000018</v>
+        <v>-4.515284800000011</v>
       </c>
       <c r="O93">
-        <v>-0.9591936960000044</v>
+        <v>-1.083668352000003</v>
       </c>
       <c r="P93">
-        <v>-3.037446704000014</v>
+        <v>-3.431616448000008</v>
       </c>
       <c r="Q93">
-        <v>5.76255329599999</v>
+        <v>5.368383551999997</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.233176784046142</v>
+        <v>1.38159888205191</v>
       </c>
       <c r="T93">
-        <v>5.83402406405099</v>
+        <v>6.563277072057364</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2196766530865192</v>
+        <v>0.217288863379057</v>
       </c>
       <c r="W93">
-        <v>0.114551467326899</v>
+        <v>0.1149019948559544</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.9153193878604966</v>
+        <v>0.9053702640794044</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2162377458316308</v>
+        <v>0.2172477458316308</v>
       </c>
       <c r="C94">
-        <v>-20.39696722293172</v>
+        <v>-25.69755840142676</v>
       </c>
       <c r="D94">
-        <v>300.0490327770683</v>
+        <v>298.2814415985733</v>
       </c>
       <c r="E94">
-        <v>243.036</v>
+        <v>246.569</v>
       </c>
       <c r="F94">
-        <v>325.036</v>
+        <v>328.569</v>
       </c>
       <c r="G94">
         <v>4.59</v>
@@ -8995,37 +8995,37 @@
         <v>43.2</v>
       </c>
       <c r="M94">
-        <v>47.71528480000001</v>
+        <v>48.23392920000001</v>
       </c>
       <c r="N94">
-        <v>-4.515284800000011</v>
+        <v>-5.03392920000001</v>
       </c>
       <c r="O94">
-        <v>-1.083668352000003</v>
+        <v>-1.208143008000002</v>
       </c>
       <c r="P94">
-        <v>-3.431616448000008</v>
+        <v>-3.825786192000008</v>
       </c>
       <c r="Q94">
-        <v>5.368383551999997</v>
+        <v>4.974213807999996</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.38159888205191</v>
+        <v>1.572427293773612</v>
       </c>
       <c r="T94">
-        <v>6.563277072057364</v>
+        <v>7.500888082351275</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.217288863379057</v>
+        <v>0.2149524239878844</v>
       </c>
       <c r="W94">
-        <v>0.1149019948559544</v>
+        <v>0.1152449841585786</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.9053702640794044</v>
+        <v>0.8956350999495183</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2172477458316308</v>
+        <v>0.2182577458316309</v>
       </c>
       <c r="C95">
-        <v>-25.69755840142676</v>
+        <v>-30.97744575961298</v>
       </c>
       <c r="D95">
-        <v>298.2814415985733</v>
+        <v>296.5345542403871</v>
       </c>
       <c r="E95">
-        <v>246.569</v>
+        <v>250.102</v>
       </c>
       <c r="F95">
-        <v>328.569</v>
+        <v>332.102</v>
       </c>
       <c r="G95">
         <v>4.59</v>
@@ -9077,37 +9077,37 @@
         <v>43.2</v>
       </c>
       <c r="M95">
-        <v>48.23392920000001</v>
+        <v>48.75257360000001</v>
       </c>
       <c r="N95">
-        <v>-5.03392920000001</v>
+        <v>-5.552573600000017</v>
       </c>
       <c r="O95">
-        <v>-1.208143008000002</v>
+        <v>-1.332617664000004</v>
       </c>
       <c r="P95">
-        <v>-3.825786192000008</v>
+        <v>-4.219955936000012</v>
       </c>
       <c r="Q95">
-        <v>4.974213807999996</v>
+        <v>4.580044063999992</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.572427293773612</v>
+        <v>1.826865176069214</v>
       </c>
       <c r="T95">
-        <v>7.500888082351275</v>
+        <v>8.75103609607649</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2149524239878844</v>
+        <v>0.2126656960731196</v>
       </c>
       <c r="W95">
-        <v>0.1152449841585786</v>
+        <v>0.1155806758164661</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8956350999495183</v>
+        <v>0.8861070669713318</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2182577458316309</v>
+        <v>0.2192677458316308</v>
       </c>
       <c r="C96">
-        <v>-30.97744575961298</v>
+        <v>-36.2369909357605</v>
       </c>
       <c r="D96">
-        <v>296.5345542403871</v>
+        <v>294.8080090642396</v>
       </c>
       <c r="E96">
-        <v>250.102</v>
+        <v>253.635</v>
       </c>
       <c r="F96">
-        <v>332.102</v>
+        <v>335.635</v>
       </c>
       <c r="G96">
         <v>4.59</v>
@@ -9159,37 +9159,37 @@
         <v>43.2</v>
       </c>
       <c r="M96">
-        <v>48.75257360000001</v>
+        <v>49.27121800000001</v>
       </c>
       <c r="N96">
-        <v>-5.552573600000017</v>
+        <v>-6.071218000000016</v>
       </c>
       <c r="O96">
-        <v>-1.332617664000004</v>
+        <v>-1.457092320000004</v>
       </c>
       <c r="P96">
-        <v>-4.219955936000012</v>
+        <v>-4.614125680000012</v>
       </c>
       <c r="Q96">
-        <v>4.580044063999992</v>
+        <v>4.185874319999992</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.826865176069214</v>
+        <v>2.183078211283057</v>
       </c>
       <c r="T96">
-        <v>8.75103609607649</v>
+        <v>10.50124331529179</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2126656960731196</v>
+        <v>0.2104271097986657</v>
       </c>
       <c r="W96">
-        <v>0.1155806758164661</v>
+        <v>0.1159093002815559</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8861070669713318</v>
+        <v>0.8767796241611073</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2192677458316308</v>
+        <v>0.2202777458316308</v>
       </c>
       <c r="C97">
-        <v>-36.2369909357605</v>
+        <v>-41.47654719447229</v>
       </c>
       <c r="D97">
-        <v>294.8080090642396</v>
+        <v>293.1014528055278</v>
       </c>
       <c r="E97">
-        <v>253.635</v>
+        <v>257.1680000000001</v>
       </c>
       <c r="F97">
-        <v>335.635</v>
+        <v>339.1680000000001</v>
       </c>
       <c r="G97">
         <v>4.59</v>
@@ -9241,37 +9241,37 @@
         <v>43.2</v>
       </c>
       <c r="M97">
-        <v>49.27121800000001</v>
+        <v>49.78986240000001</v>
       </c>
       <c r="N97">
-        <v>-6.071218000000016</v>
+        <v>-6.589862400000015</v>
       </c>
       <c r="O97">
-        <v>-1.457092320000004</v>
+        <v>-1.581566976000004</v>
       </c>
       <c r="P97">
-        <v>-4.614125680000012</v>
+        <v>-5.008295424000011</v>
       </c>
       <c r="Q97">
-        <v>4.185874319999992</v>
+        <v>3.791704575999993</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.183078211283057</v>
+        <v>2.717397764103823</v>
       </c>
       <c r="T97">
-        <v>10.50124331529179</v>
+        <v>13.12655414411475</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2104271097986657</v>
+        <v>0.208235160738263</v>
       </c>
       <c r="W97">
-        <v>0.1159093002815559</v>
+        <v>0.116231078403623</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8767796241611073</v>
+        <v>0.8676465030760958</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2202777458316308</v>
+        <v>0.2212877458316308</v>
       </c>
       <c r="C98">
-        <v>-41.47654719447218</v>
+        <v>-46.69645966765194</v>
       </c>
       <c r="D98">
-        <v>293.1014528055279</v>
+        <v>291.4145403323481</v>
       </c>
       <c r="E98">
-        <v>257.168</v>
+        <v>260.701</v>
       </c>
       <c r="F98">
-        <v>339.168</v>
+        <v>342.701</v>
       </c>
       <c r="G98">
         <v>4.59</v>
@@ -9323,37 +9323,37 @@
         <v>43.2</v>
       </c>
       <c r="M98">
-        <v>49.7898624</v>
+        <v>50.30850680000001</v>
       </c>
       <c r="N98">
-        <v>-6.589862400000008</v>
+        <v>-7.108506800000015</v>
       </c>
       <c r="O98">
-        <v>-1.581566976000002</v>
+        <v>-1.706041632000004</v>
       </c>
       <c r="P98">
-        <v>-5.008295424000006</v>
+        <v>-5.402465168000012</v>
       </c>
       <c r="Q98">
-        <v>3.791704575999998</v>
+        <v>3.397534831999993</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.717397764103816</v>
+        <v>3.607930352138422</v>
       </c>
       <c r="T98">
-        <v>13.12655414411471</v>
+        <v>17.50207219215295</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.208235160738263</v>
+        <v>0.2060884065038479</v>
       </c>
       <c r="W98">
-        <v>0.116231078403623</v>
+        <v>0.1165462219252351</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8676465030760959</v>
+        <v>0.858701693766033</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2212877458316308</v>
+        <v>0.2222977458316308</v>
       </c>
       <c r="C99">
-        <v>-46.69645966765194</v>
+        <v>-51.89706558719973</v>
       </c>
       <c r="D99">
-        <v>291.4145403323481</v>
+        <v>289.7469344128003</v>
       </c>
       <c r="E99">
-        <v>260.701</v>
+        <v>264.234</v>
       </c>
       <c r="F99">
-        <v>342.701</v>
+        <v>346.234</v>
       </c>
       <c r="G99">
         <v>4.59</v>
@@ -9405,37 +9405,37 @@
         <v>43.2</v>
       </c>
       <c r="M99">
-        <v>50.30850680000001</v>
+        <v>50.8271512</v>
       </c>
       <c r="N99">
-        <v>-7.108506800000015</v>
+        <v>-7.627151200000007</v>
       </c>
       <c r="O99">
-        <v>-1.706041632000004</v>
+        <v>-1.830516288000002</v>
       </c>
       <c r="P99">
-        <v>-5.402465168000012</v>
+        <v>-5.796634912000005</v>
       </c>
       <c r="Q99">
-        <v>3.397534831999993</v>
+        <v>3.003365087999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.607930352138422</v>
+        <v>5.388995528207632</v>
       </c>
       <c r="T99">
-        <v>17.50207219215295</v>
+        <v>26.25310828822942</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2060884065038479</v>
+        <v>0.2039854635803393</v>
       </c>
       <c r="W99">
-        <v>0.1165462219252351</v>
+        <v>0.1168549339464062</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.858701693766033</v>
+        <v>0.8499394315847471</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2222977458316308</v>
+        <v>0.2233077458316308</v>
       </c>
       <c r="C100">
-        <v>-51.89706558719973</v>
+        <v>-57.07869450976244</v>
       </c>
       <c r="D100">
-        <v>289.7469344128003</v>
+        <v>288.0983054902376</v>
       </c>
       <c r="E100">
-        <v>264.234</v>
+        <v>267.767</v>
       </c>
       <c r="F100">
-        <v>346.234</v>
+        <v>349.767</v>
       </c>
       <c r="G100">
         <v>4.59</v>
@@ -9487,37 +9487,37 @@
         <v>43.2</v>
       </c>
       <c r="M100">
-        <v>50.8271512</v>
+        <v>51.3457956</v>
       </c>
       <c r="N100">
-        <v>-7.627151200000007</v>
+        <v>-8.145795600000007</v>
       </c>
       <c r="O100">
-        <v>-1.830516288000002</v>
+        <v>-1.954990944000002</v>
       </c>
       <c r="P100">
-        <v>-5.796634912000005</v>
+        <v>-6.190804656000005</v>
       </c>
       <c r="Q100">
-        <v>3.003365087999999</v>
+        <v>2.609195343999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.388995528207632</v>
+        <v>10.73219105641526</v>
       </c>
       <c r="T100">
-        <v>26.25310828822942</v>
+        <v>52.50621657645884</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2039854635803393</v>
+        <v>0.201925004352255</v>
       </c>
       <c r="W100">
-        <v>0.1168549339464062</v>
+        <v>0.117157409361089</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8499394315847471</v>
+        <v>0.8413541848010627</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2233077458316308</v>
-      </c>
-      <c r="C101">
-        <v>-57.07869450976244</v>
-      </c>
-      <c r="D101">
-        <v>288.0983054902376</v>
-      </c>
-      <c r="E101">
-        <v>267.767</v>
-      </c>
-      <c r="F101">
-        <v>349.767</v>
-      </c>
-      <c r="G101">
-        <v>4.59</v>
-      </c>
-      <c r="H101">
-        <v>271.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>52</v>
-      </c>
-      <c r="K101">
-        <v>8.800000000000004</v>
-      </c>
-      <c r="L101">
-        <v>43.2</v>
-      </c>
-      <c r="M101">
-        <v>51.3457956</v>
-      </c>
-      <c r="N101">
-        <v>-8.145795600000007</v>
-      </c>
-      <c r="O101">
-        <v>-1.954990944000002</v>
-      </c>
-      <c r="P101">
-        <v>-6.190804656000005</v>
-      </c>
-      <c r="Q101">
-        <v>2.609195343999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>10.73219105641526</v>
-      </c>
-      <c r="T101">
-        <v>52.50621657645884</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.201925004352255</v>
-      </c>
-      <c r="W101">
-        <v>0.117157409361089</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8413541848010627</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
